--- a/s60_signal/position-2319-151-800.xlsx
+++ b/s60_signal/position-2319-151-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2893" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2896" uniqueCount="793">
   <si>
     <t>trade_time</t>
   </si>
@@ -1405,7 +1405,7 @@
     <t>2021-04-13</t>
   </si>
   <si>
-    <t>2021-07-22</t>
+    <t>2021-07-23</t>
   </si>
   <si>
     <t>2010-03-04</t>
@@ -2750,7 +2750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P971"/>
+  <dimension ref="A1:P972"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -50030,96 +50030,96 @@
     </row>
     <row r="960" spans="1:16">
       <c r="A960" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B960" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C960">
-        <v>2.025162321012973</v>
+        <v>3.138215786977653</v>
       </c>
       <c r="D960" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E960">
-        <v>2.748951126188311</v>
+        <v>2.502201575787621</v>
       </c>
       <c r="F960">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G960">
-        <v>0.009154837678987027</v>
+        <v>0.009241784213022347</v>
       </c>
       <c r="H960">
-        <v>0.009131048873811687</v>
+        <v>0.008777798424212379</v>
       </c>
       <c r="I960">
-        <v>0.7237888051753383</v>
+        <v>0.6360142111900329</v>
       </c>
       <c r="J960">
-        <v>0.06922014910654421</v>
+        <v>0.06881136895202586</v>
       </c>
       <c r="K960">
-        <v>51.5</v>
+        <v>44.35</v>
       </c>
       <c r="L960">
-        <v>5.59</v>
+        <v>6.19</v>
       </c>
       <c r="M960">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N960">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O960">
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
     </row>
     <row r="961" spans="1:16">
       <c r="A961" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B961" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C961">
-        <v>3.218116050648887</v>
+        <v>2.025162321012973</v>
       </c>
       <c r="D961" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E961">
-        <v>2.483561200741584</v>
+        <v>2.748951126188311</v>
       </c>
       <c r="F961">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G961">
-        <v>0.008741883949351116</v>
+        <v>0.009154837678987027</v>
       </c>
       <c r="H961">
-        <v>0.008796438799258417</v>
+        <v>0.009131048873811687</v>
       </c>
       <c r="I961">
-        <v>0.7345548499073029</v>
+        <v>0.7237888051753383</v>
       </c>
       <c r="J961">
         <v>0.06922014910654421</v>
       </c>
       <c r="K961">
-        <v>39.9</v>
+        <v>51.5</v>
       </c>
       <c r="L961">
-        <v>5.98</v>
+        <v>5.59</v>
       </c>
       <c r="M961">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="N961">
-        <v>5.64</v>
+        <v>5.94</v>
       </c>
       <c r="O961">
         <v>1</v>
@@ -50130,96 +50130,96 @@
     </row>
     <row r="962" spans="1:16">
       <c r="A962" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B962" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C962">
-        <v>2.047715219225316</v>
+        <v>3.218116050648887</v>
       </c>
       <c r="D962" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E962">
-        <v>2.769139254491011</v>
+        <v>2.483561200741584</v>
       </c>
       <c r="F962">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G962">
-        <v>0.009132284780774682</v>
+        <v>0.008741883949351116</v>
       </c>
       <c r="H962">
-        <v>0.009110860745508988</v>
+        <v>0.008796438799258417</v>
       </c>
       <c r="I962">
-        <v>0.7214240352656947</v>
+        <v>0.7345548499073029</v>
       </c>
       <c r="J962">
-        <v>0.06878222875290647</v>
+        <v>0.06922014910654421</v>
       </c>
       <c r="K962">
-        <v>51.5</v>
+        <v>39.9</v>
       </c>
       <c r="L962">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
       <c r="M962">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N962">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O962">
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="963" spans="1:16">
       <c r="A963" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B963" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C963">
-        <v>3.235589072759032</v>
+        <v>2.047715219225316</v>
       </c>
       <c r="D963" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E963">
-        <v>2.503530368867464</v>
+        <v>2.769139254491011</v>
       </c>
       <c r="F963">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G963">
-        <v>0.00872441092724097</v>
+        <v>0.009132284780774682</v>
       </c>
       <c r="H963">
-        <v>0.008776469631132535</v>
+        <v>0.009110860745508988</v>
       </c>
       <c r="I963">
-        <v>0.732058703891568</v>
+        <v>0.7214240352656947</v>
       </c>
       <c r="J963">
         <v>0.06878222875290647</v>
       </c>
       <c r="K963">
-        <v>39.9</v>
+        <v>51.5</v>
       </c>
       <c r="L963">
-        <v>5.98</v>
+        <v>5.59</v>
       </c>
       <c r="M963">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="N963">
-        <v>5.64</v>
+        <v>5.94</v>
       </c>
       <c r="O963">
         <v>1</v>
@@ -50230,99 +50230,99 @@
     </row>
     <row r="964" spans="1:16">
       <c r="A964" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B964" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C964">
-        <v>6.518598702106193</v>
+        <v>3.235589072759032</v>
       </c>
       <c r="D964" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E964">
-        <v>6.052303309796228</v>
+        <v>2.503530368867464</v>
       </c>
       <c r="F964">
         <v>-1</v>
       </c>
       <c r="G964">
-        <v>0.005861401297893808</v>
+        <v>0.00872441092724097</v>
       </c>
       <c r="H964">
-        <v>0.005387696690203772</v>
+        <v>0.008776469631132535</v>
       </c>
       <c r="I964">
-        <v>0.4662953923099646</v>
+        <v>0.732058703891568</v>
       </c>
       <c r="J964">
-        <v>-0.007409215380071977</v>
+        <v>0.06878222875290647</v>
       </c>
       <c r="K964">
-        <v>44.35</v>
+        <v>39.9</v>
       </c>
       <c r="L964">
-        <v>6.19</v>
+        <v>5.98</v>
       </c>
       <c r="M964">
-        <v>44.85</v>
+        <v>45.6</v>
       </c>
       <c r="N964">
-        <v>5.72</v>
+        <v>5.64</v>
       </c>
       <c r="O964">
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="965" spans="1:16">
       <c r="A965" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B965" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C965">
-        <v>5.686375937492171</v>
+        <v>6.518598702106193</v>
       </c>
       <c r="D965" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E965">
-        <v>5.768228241337189</v>
+        <v>6.052303309796228</v>
       </c>
       <c r="F965">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G965">
-        <v>0.00503362406250783</v>
+        <v>0.005861401297893808</v>
       </c>
       <c r="H965">
-        <v>0.005111771758662812</v>
+        <v>0.005387696690203772</v>
       </c>
       <c r="I965">
-        <v>0.08185230384501807</v>
+        <v>0.4662953923099646</v>
       </c>
       <c r="J965">
         <v>-0.007409215380071977</v>
       </c>
       <c r="K965">
-        <v>44.05</v>
+        <v>44.35</v>
       </c>
       <c r="L965">
-        <v>5.36</v>
+        <v>6.19</v>
       </c>
       <c r="M965">
-        <v>44.3</v>
+        <v>44.85</v>
       </c>
       <c r="N965">
-        <v>5.44</v>
+        <v>5.72</v>
       </c>
       <c r="O965">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P965" t="s">
         <v>789</v>
@@ -50330,99 +50330,99 @@
     </row>
     <row r="966" spans="1:16">
       <c r="A966" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B966" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C966">
-        <v>6.991566556621656</v>
+        <v>5.686375937492171</v>
       </c>
       <c r="D966" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E966">
-        <v>6.530603383641066</v>
+        <v>5.745635015954163</v>
       </c>
       <c r="F966">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G966">
-        <v>0.005388433443378345</v>
+        <v>0.00503362406250783</v>
       </c>
       <c r="H966">
-        <v>0.004909396616358934</v>
+        <v>0.005094364984045837</v>
       </c>
       <c r="I966">
-        <v>0.4609631729805903</v>
+        <v>0.05925907846199241</v>
       </c>
       <c r="J966">
-        <v>-0.01807365403881975</v>
+        <v>-0.007409215380071977</v>
       </c>
       <c r="K966">
-        <v>44.35</v>
+        <v>44.05</v>
       </c>
       <c r="L966">
-        <v>6.19</v>
+        <v>5.36</v>
       </c>
       <c r="M966">
-        <v>44.85</v>
+        <v>43.95</v>
       </c>
       <c r="N966">
-        <v>5.72</v>
+        <v>5.42</v>
       </c>
       <c r="O966">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P966" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="967" spans="1:16">
       <c r="A967" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B967" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C967">
-        <v>6.15614446041001</v>
+        <v>6.991566556621656</v>
       </c>
       <c r="D967" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E967">
-        <v>6.240662873919716</v>
+        <v>6.530603383641066</v>
       </c>
       <c r="F967">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G967">
-        <v>0.004563855539589991</v>
+        <v>0.005388433443378345</v>
       </c>
       <c r="H967">
-        <v>0.004639337126080285</v>
+        <v>0.004909396616358934</v>
       </c>
       <c r="I967">
-        <v>0.08451841350970568</v>
+        <v>0.4609631729805903</v>
       </c>
       <c r="J967">
         <v>-0.01807365403881975</v>
       </c>
       <c r="K967">
-        <v>44.05</v>
+        <v>44.35</v>
       </c>
       <c r="L967">
-        <v>5.36</v>
+        <v>6.19</v>
       </c>
       <c r="M967">
-        <v>44.3</v>
+        <v>44.85</v>
       </c>
       <c r="N967">
-        <v>5.44</v>
+        <v>5.72</v>
       </c>
       <c r="O967">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P967" t="s">
         <v>790</v>
@@ -50430,99 +50430,99 @@
     </row>
     <row r="968" spans="1:16">
       <c r="A968" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B968" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C968">
-        <v>7.158772656458988</v>
+        <v>6.15614446041001</v>
       </c>
       <c r="D968" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E968">
-        <v>6.699694557884682</v>
+        <v>6.214337095006128</v>
       </c>
       <c r="F968">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G968">
-        <v>0.005221227343541013</v>
+        <v>0.004563855539589991</v>
       </c>
       <c r="H968">
-        <v>0.004740305442115318</v>
+        <v>0.004625662904993872</v>
       </c>
       <c r="I968">
-        <v>0.4590780985743068</v>
+        <v>0.0581926345961179</v>
       </c>
       <c r="J968">
-        <v>-0.02184380285138643</v>
+        <v>-0.01807365403881975</v>
       </c>
       <c r="K968">
-        <v>44.35</v>
+        <v>44.05</v>
       </c>
       <c r="L968">
-        <v>6.19</v>
+        <v>5.36</v>
       </c>
       <c r="M968">
-        <v>44.85</v>
+        <v>43.95</v>
       </c>
       <c r="N968">
-        <v>5.72</v>
+        <v>5.42</v>
       </c>
       <c r="O968">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P968" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="969" spans="1:16">
       <c r="A969" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B969" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C969">
-        <v>6.322219515603573</v>
+        <v>7.158772656458988</v>
       </c>
       <c r="D969" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="E969">
-        <v>6.407680466316419</v>
+        <v>6.699694557884682</v>
       </c>
       <c r="F969">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G969">
-        <v>0.004397780484396428</v>
+        <v>0.005221227343541013</v>
       </c>
       <c r="H969">
-        <v>0.004472319533683581</v>
+        <v>0.004740305442115318</v>
       </c>
       <c r="I969">
-        <v>0.08546095071284654</v>
+        <v>0.4590780985743068</v>
       </c>
       <c r="J969">
         <v>-0.02184380285138643</v>
       </c>
       <c r="K969">
-        <v>44.05</v>
+        <v>44.35</v>
       </c>
       <c r="L969">
-        <v>5.36</v>
+        <v>6.19</v>
       </c>
       <c r="M969">
-        <v>44.3</v>
+        <v>44.85</v>
       </c>
       <c r="N969">
-        <v>5.44</v>
+        <v>5.72</v>
       </c>
       <c r="O969">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P969" t="s">
         <v>791</v>
@@ -50530,34 +50530,34 @@
     </row>
     <row r="970" spans="1:16">
       <c r="A970" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B970" t="s">
         <v>222</v>
       </c>
       <c r="C970">
-        <v>6.34308163058533</v>
+        <v>6.322219515603573</v>
       </c>
       <c r="D970" t="s">
         <v>463</v>
       </c>
       <c r="E970">
-        <v>6.428660981496711</v>
+        <v>6.380035135318433</v>
       </c>
       <c r="F970">
         <v>1</v>
       </c>
       <c r="G970">
-        <v>0.00437691836941467</v>
+        <v>0.004397780484396428</v>
       </c>
       <c r="H970">
-        <v>0.00445133901850329</v>
+        <v>0.004459964864681567</v>
       </c>
       <c r="I970">
-        <v>0.08557935091138091</v>
+        <v>0.05781561971486049</v>
       </c>
       <c r="J970">
-        <v>-0.02231740364552396</v>
+        <v>-0.02184380285138643</v>
       </c>
       <c r="K970">
         <v>44.05</v>
@@ -50566,16 +50566,16 @@
         <v>5.36</v>
       </c>
       <c r="M970">
-        <v>44.3</v>
+        <v>43.95</v>
       </c>
       <c r="N970">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="O970">
         <v>0</v>
       </c>
       <c r="P970" t="s">
-        <v>221</v>
+        <v>791</v>
       </c>
     </row>
     <row r="971" spans="1:16">
@@ -50586,28 +50586,28 @@
         <v>222</v>
       </c>
       <c r="C971">
-        <v>6.311554267650159</v>
+        <v>6.34308163058533</v>
       </c>
       <c r="D971" t="s">
         <v>463</v>
       </c>
       <c r="E971">
-        <v>6.396954689146471</v>
+        <v>6.400849890220778</v>
       </c>
       <c r="F971">
         <v>1</v>
       </c>
       <c r="G971">
-        <v>0.004408445732349842</v>
+        <v>0.00437691836941467</v>
       </c>
       <c r="H971">
-        <v>0.00448304531085353</v>
+        <v>0.004439150109779222</v>
       </c>
       <c r="I971">
-        <v>0.08540042149631155</v>
+        <v>0.05776825963544763</v>
       </c>
       <c r="J971">
-        <v>-0.02160168598524764</v>
+        <v>-0.02231740364552396</v>
       </c>
       <c r="K971">
         <v>44.05</v>
@@ -50616,15 +50616,65 @@
         <v>5.36</v>
       </c>
       <c r="M971">
-        <v>44.3</v>
+        <v>43.95</v>
       </c>
       <c r="N971">
-        <v>5.44</v>
+        <v>5.42</v>
       </c>
       <c r="O971">
         <v>0</v>
       </c>
       <c r="P971" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="972" spans="1:16">
+      <c r="A972" s="1">
+        <v>0</v>
+      </c>
+      <c r="B972" t="s">
+        <v>222</v>
+      </c>
+      <c r="C972">
+        <v>6.311554267650159</v>
+      </c>
+      <c r="D972" t="s">
+        <v>463</v>
+      </c>
+      <c r="E972">
+        <v>6.369394099051633</v>
+      </c>
+      <c r="F972">
+        <v>1</v>
+      </c>
+      <c r="G972">
+        <v>0.004408445732349842</v>
+      </c>
+      <c r="H972">
+        <v>0.004470605900948367</v>
+      </c>
+      <c r="I972">
+        <v>0.05783983140147431</v>
+      </c>
+      <c r="J972">
+        <v>-0.02160168598524764</v>
+      </c>
+      <c r="K972">
+        <v>44.05</v>
+      </c>
+      <c r="L972">
+        <v>5.36</v>
+      </c>
+      <c r="M972">
+        <v>43.95</v>
+      </c>
+      <c r="N972">
+        <v>5.42</v>
+      </c>
+      <c r="O972">
+        <v>0</v>
+      </c>
+      <c r="P972" t="s">
         <v>792</v>
       </c>
     </row>

--- a/s60_signal/position-2319-151-800.xlsx
+++ b/s60_signal/position-2319-151-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2896" uniqueCount="793">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2905" uniqueCount="794">
   <si>
     <t>trade_time</t>
   </si>
@@ -682,7 +682,7 @@
     <t>2021-03-19</t>
   </si>
   <si>
-    <t>2021-07-12</t>
+    <t>2021-07-27</t>
   </si>
   <si>
     <t>2010-12-20</t>
@@ -1405,7 +1405,10 @@
     <t>2021-04-13</t>
   </si>
   <si>
-    <t>2021-07-23</t>
+    <t>2021-07-29</t>
+  </si>
+  <si>
+    <t>2021-04-26</t>
   </si>
   <si>
     <t>2010-03-04</t>
@@ -2750,7 +2753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P972"/>
+  <dimension ref="A1:P975"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2847,7 +2850,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2897,7 +2900,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2947,7 +2950,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -2997,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -3047,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -3097,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3147,7 +3150,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -3197,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3247,7 +3250,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3297,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3347,7 +3350,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3397,7 +3400,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3447,7 +3450,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3497,7 +3500,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3547,7 +3550,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3597,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3647,7 +3650,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3697,7 +3700,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3747,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3797,7 +3800,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3847,7 +3850,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3897,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3947,7 +3950,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -3997,7 +4000,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -4047,7 +4050,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -4097,7 +4100,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -4147,7 +4150,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4197,7 +4200,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -4247,7 +4250,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4297,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4347,7 +4350,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4397,7 +4400,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4447,7 +4450,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4497,7 +4500,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4547,7 +4550,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4597,7 +4600,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4697,7 +4700,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4747,7 +4750,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4847,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4897,7 +4900,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4947,7 +4950,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -4997,7 +5000,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -5047,7 +5050,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -5097,7 +5100,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -5147,7 +5150,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -5197,7 +5200,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5247,7 +5250,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5297,7 +5300,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5347,7 +5350,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5397,7 +5400,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5447,7 +5450,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5497,7 +5500,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5547,7 +5550,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5597,7 +5600,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5647,7 +5650,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5697,7 +5700,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5747,7 +5750,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5797,7 +5800,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5847,7 +5850,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5897,7 +5900,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5947,7 +5950,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -5997,7 +6000,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -6047,7 +6050,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -6097,7 +6100,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -6147,7 +6150,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -6197,7 +6200,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -6247,7 +6250,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -6297,7 +6300,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6347,7 +6350,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6397,7 +6400,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6447,7 +6450,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6497,7 +6500,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6547,7 +6550,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6597,7 +6600,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6647,7 +6650,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6697,7 +6700,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6747,7 +6750,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6797,7 +6800,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6847,7 +6850,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6897,7 +6900,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6947,7 +6950,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -6997,7 +7000,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -7047,7 +7050,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -7097,7 +7100,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -7147,7 +7150,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -7347,7 +7350,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -7397,7 +7400,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -7447,7 +7450,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -7497,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -7547,7 +7550,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7597,7 +7600,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7647,7 +7650,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7697,7 +7700,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7747,7 +7750,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7797,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7847,7 +7850,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7897,7 +7900,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7947,7 +7950,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -7997,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -8047,7 +8050,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -8097,7 +8100,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -8147,7 +8150,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -8197,7 +8200,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -8247,7 +8250,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -8276,7 +8279,7 @@
         <v>8</v>
       </c>
       <c r="P111" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -8305,7 +8308,7 @@
         <v>7.75</v>
       </c>
       <c r="P112" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -8334,7 +8337,7 @@
         <v>7.82</v>
       </c>
       <c r="P113" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8384,7 +8387,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -8434,7 +8437,7 @@
         <v>0</v>
       </c>
       <c r="P115" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -8484,7 +8487,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8534,7 +8537,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8584,7 +8587,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8634,7 +8637,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8684,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8734,7 +8737,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8784,7 +8787,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8834,7 +8837,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8884,7 +8887,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8934,7 +8937,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8984,7 +8987,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -9034,7 +9037,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -9084,7 +9087,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -9134,7 +9137,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9184,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9234,7 +9237,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -9284,7 +9287,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -9334,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -9384,7 +9387,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -9434,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -9484,7 +9487,7 @@
         <v>0</v>
       </c>
       <c r="P136" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9534,7 +9537,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9584,7 +9587,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9634,7 +9637,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9684,7 +9687,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9734,7 +9737,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9784,7 +9787,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9834,7 +9837,7 @@
         <v>0</v>
       </c>
       <c r="P143" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9884,7 +9887,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9934,7 +9937,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9984,7 +9987,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -10034,7 +10037,7 @@
         <v>0</v>
       </c>
       <c r="P147" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -10084,7 +10087,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -10134,7 +10137,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -10184,7 +10187,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -10234,7 +10237,7 @@
         <v>0</v>
       </c>
       <c r="P151" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -10284,7 +10287,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -10334,7 +10337,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10384,7 +10387,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10434,7 +10437,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10484,7 +10487,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10534,7 +10537,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10584,7 +10587,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10634,7 +10637,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10684,7 +10687,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10713,7 +10716,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="P161" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10742,7 +10745,7 @@
         <v>8.83</v>
       </c>
       <c r="P162" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10771,7 +10774,7 @@
         <v>9.27</v>
       </c>
       <c r="P163" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10821,7 +10824,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10871,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="P165" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10921,7 +10924,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10971,7 +10974,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -11021,7 +11024,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -11071,7 +11074,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -11121,7 +11124,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11171,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="P171" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -11221,7 +11224,7 @@
         <v>0</v>
       </c>
       <c r="P172" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -11271,7 +11274,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -11321,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="P174" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -11371,7 +11374,7 @@
         <v>0</v>
       </c>
       <c r="P175" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -11421,7 +11424,7 @@
         <v>0</v>
       </c>
       <c r="P176" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11471,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="P177" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11521,7 +11524,7 @@
         <v>0</v>
       </c>
       <c r="P178" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11571,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="P179" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11621,7 +11624,7 @@
         <v>0</v>
       </c>
       <c r="P180" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11671,7 +11674,7 @@
         <v>0</v>
       </c>
       <c r="P181" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11721,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="P182" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11771,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="P183" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11821,7 +11824,7 @@
         <v>0</v>
       </c>
       <c r="P184" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11871,7 +11874,7 @@
         <v>0</v>
       </c>
       <c r="P185" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11921,7 +11924,7 @@
         <v>0</v>
       </c>
       <c r="P186" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11971,7 +11974,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -12021,7 +12024,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -12071,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -12121,7 +12124,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -12171,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -12221,7 +12224,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -12271,7 +12274,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -12471,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -12521,7 +12524,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -12571,7 +12574,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12621,7 +12624,7 @@
         <v>0</v>
       </c>
       <c r="P200" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -12671,7 +12674,7 @@
         <v>0</v>
       </c>
       <c r="P201" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12721,7 +12724,7 @@
         <v>0</v>
       </c>
       <c r="P202" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12771,7 +12774,7 @@
         <v>0</v>
       </c>
       <c r="P203" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12821,7 +12824,7 @@
         <v>0</v>
       </c>
       <c r="P204" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12871,7 +12874,7 @@
         <v>0</v>
       </c>
       <c r="P205" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12921,7 +12924,7 @@
         <v>0</v>
       </c>
       <c r="P206" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12971,7 +12974,7 @@
         <v>0</v>
       </c>
       <c r="P207" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -14121,7 +14124,7 @@
         <v>0</v>
       </c>
       <c r="P230" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14171,7 +14174,7 @@
         <v>0</v>
       </c>
       <c r="P231" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14221,7 +14224,7 @@
         <v>0</v>
       </c>
       <c r="P232" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14271,7 +14274,7 @@
         <v>0</v>
       </c>
       <c r="P233" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14321,7 +14324,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14371,7 +14374,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14421,7 +14424,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14471,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -14521,7 +14524,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14571,7 +14574,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -14621,7 +14624,7 @@
         <v>0</v>
       </c>
       <c r="P240" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14671,7 +14674,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14721,7 +14724,7 @@
         <v>0</v>
       </c>
       <c r="P242" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14771,7 +14774,7 @@
         <v>0</v>
       </c>
       <c r="P243" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14821,7 +14824,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14850,7 +14853,7 @@
         <v>10.56</v>
       </c>
       <c r="P245" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14879,7 +14882,7 @@
         <v>10.44</v>
       </c>
       <c r="P246" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14908,7 +14911,7 @@
         <v>10.38</v>
       </c>
       <c r="P247" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14937,7 +14940,7 @@
         <v>10.74</v>
       </c>
       <c r="P248" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14987,7 +14990,7 @@
         <v>0</v>
       </c>
       <c r="P249" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15037,7 +15040,7 @@
         <v>0</v>
       </c>
       <c r="P250" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15087,7 +15090,7 @@
         <v>0</v>
       </c>
       <c r="P251" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -15137,7 +15140,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -15187,7 +15190,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -15237,7 +15240,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -15287,7 +15290,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -15337,7 +15340,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -15387,7 +15390,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -15437,7 +15440,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -15487,7 +15490,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -15537,7 +15540,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -15587,7 +15590,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15637,7 +15640,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15687,7 +15690,7 @@
         <v>0</v>
       </c>
       <c r="P263" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15737,7 +15740,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15787,7 +15790,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15837,7 +15840,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15887,7 +15890,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15937,7 +15940,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15987,7 +15990,7 @@
         <v>0</v>
       </c>
       <c r="P269" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -16016,7 +16019,7 @@
         <v>11.5</v>
       </c>
       <c r="P270" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -16045,7 +16048,7 @@
         <v>11.36</v>
       </c>
       <c r="P271" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16074,7 +16077,7 @@
         <v>11.22</v>
       </c>
       <c r="P272" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16103,7 +16106,7 @@
         <v>11.08</v>
       </c>
       <c r="P273" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16153,7 +16156,7 @@
         <v>0</v>
       </c>
       <c r="P274" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -16203,7 +16206,7 @@
         <v>0</v>
       </c>
       <c r="P275" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -16253,7 +16256,7 @@
         <v>0</v>
       </c>
       <c r="P276" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -16453,7 +16456,7 @@
         <v>0</v>
       </c>
       <c r="P280" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16503,7 +16506,7 @@
         <v>0</v>
       </c>
       <c r="P281" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -16553,7 +16556,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -16703,7 +16706,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16753,7 +16756,7 @@
         <v>0</v>
       </c>
       <c r="P286" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16803,7 +16806,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16853,7 +16856,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16903,7 +16906,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16953,7 +16956,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -17003,7 +17006,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17053,7 +17056,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17103,7 +17106,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17153,7 +17156,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -17203,7 +17206,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -17253,7 +17256,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -17303,7 +17306,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -17353,7 +17356,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17403,7 +17406,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17453,7 +17456,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17503,7 +17506,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17553,7 +17556,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17603,7 +17606,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17653,7 +17656,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17703,7 +17706,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17753,7 +17756,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17803,7 +17806,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17853,7 +17856,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17903,7 +17906,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17953,7 +17956,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -18003,7 +18006,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -18053,7 +18056,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -18103,7 +18106,7 @@
         <v>0</v>
       </c>
       <c r="P313" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -18153,7 +18156,7 @@
         <v>0</v>
       </c>
       <c r="P314" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -18203,7 +18206,7 @@
         <v>0</v>
       </c>
       <c r="P315" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -18253,7 +18256,7 @@
         <v>0</v>
       </c>
       <c r="P316" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -18303,7 +18306,7 @@
         <v>0</v>
       </c>
       <c r="P317" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -18353,7 +18356,7 @@
         <v>0</v>
       </c>
       <c r="P318" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -18403,7 +18406,7 @@
         <v>0</v>
       </c>
       <c r="P319" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18453,7 +18456,7 @@
         <v>0</v>
       </c>
       <c r="P320" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18503,7 +18506,7 @@
         <v>0</v>
       </c>
       <c r="P321" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -18553,7 +18556,7 @@
         <v>0</v>
       </c>
       <c r="P322" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18753,7 +18756,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18803,7 +18806,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18853,7 +18856,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -19103,7 +19106,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -19153,7 +19156,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -19203,7 +19206,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -19253,7 +19256,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -19303,7 +19306,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -19353,7 +19356,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19403,7 +19406,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19453,7 +19456,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19503,7 +19506,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19553,7 +19556,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19603,7 +19606,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19653,7 +19656,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19703,7 +19706,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19753,7 +19756,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19803,7 +19806,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19853,7 +19856,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19903,7 +19906,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19953,7 +19956,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -20003,7 +20006,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -20053,7 +20056,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20103,7 +20106,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -20153,7 +20156,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -20203,7 +20206,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20253,7 +20256,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20303,7 +20306,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -20353,7 +20356,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20403,7 +20406,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20553,7 +20556,7 @@
         <v>0</v>
       </c>
       <c r="P362" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20603,7 +20606,7 @@
         <v>0</v>
       </c>
       <c r="P363" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20653,7 +20656,7 @@
         <v>0</v>
       </c>
       <c r="P364" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20703,7 +20706,7 @@
         <v>0</v>
       </c>
       <c r="P365" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20753,7 +20756,7 @@
         <v>0</v>
       </c>
       <c r="P366" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20803,7 +20806,7 @@
         <v>0</v>
       </c>
       <c r="P367" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20853,7 +20856,7 @@
         <v>0</v>
       </c>
       <c r="P368" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20903,7 +20906,7 @@
         <v>0</v>
       </c>
       <c r="P369" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20953,7 +20956,7 @@
         <v>0</v>
       </c>
       <c r="P370" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -21003,7 +21006,7 @@
         <v>0</v>
       </c>
       <c r="P371" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21453,7 +21456,7 @@
         <v>0</v>
       </c>
       <c r="P380" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21503,7 +21506,7 @@
         <v>0</v>
       </c>
       <c r="P381" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21553,7 +21556,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21603,7 +21606,7 @@
         <v>0</v>
       </c>
       <c r="P383" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21653,7 +21656,7 @@
         <v>0</v>
       </c>
       <c r="P384" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21703,7 +21706,7 @@
         <v>0</v>
       </c>
       <c r="P385" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21753,7 +21756,7 @@
         <v>0</v>
       </c>
       <c r="P386" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21803,7 +21806,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21853,7 +21856,7 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21903,7 +21906,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21953,7 +21956,7 @@
         <v>0</v>
       </c>
       <c r="P390" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -22003,7 +22006,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22053,7 +22056,7 @@
         <v>0</v>
       </c>
       <c r="P392" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22103,7 +22106,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22153,7 +22156,7 @@
         <v>0</v>
       </c>
       <c r="P394" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22203,7 +22206,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22253,7 +22256,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22303,7 +22306,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22353,7 +22356,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22403,7 +22406,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22453,7 +22456,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22503,7 +22506,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22553,7 +22556,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22603,7 +22606,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22653,7 +22656,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22703,7 +22706,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22753,7 +22756,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22803,7 +22806,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22853,7 +22856,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22953,7 +22956,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23003,7 +23006,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23053,7 +23056,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23103,7 +23106,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23153,7 +23156,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23203,7 +23206,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23253,7 +23256,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23303,7 +23306,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23353,7 +23356,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23403,7 +23406,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23453,7 +23456,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23503,7 +23506,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23553,7 +23556,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23603,7 +23606,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23653,7 +23656,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23703,7 +23706,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23753,7 +23756,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23803,7 +23806,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23832,7 +23835,7 @@
         <v>5.49</v>
       </c>
       <c r="P428" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23882,7 +23885,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23932,7 +23935,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23982,7 +23985,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24032,7 +24035,7 @@
         <v>0</v>
       </c>
       <c r="P432" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24082,7 +24085,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24132,7 +24135,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -24182,7 +24185,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24232,7 +24235,7 @@
         <v>0</v>
       </c>
       <c r="P436" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24282,7 +24285,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24332,7 +24335,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24382,7 +24385,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24432,7 +24435,7 @@
         <v>0</v>
       </c>
       <c r="P440" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24482,7 +24485,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24532,7 +24535,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24582,7 +24585,7 @@
         <v>0</v>
       </c>
       <c r="P443" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24632,7 +24635,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24682,7 +24685,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24732,7 +24735,7 @@
         <v>0</v>
       </c>
       <c r="P446" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24782,7 +24785,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24832,7 +24835,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24882,7 +24885,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24932,7 +24935,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24982,7 +24985,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25032,7 +25035,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25082,7 +25085,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25132,7 +25135,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25182,7 +25185,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25232,7 +25235,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25282,7 +25285,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -25332,7 +25335,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -25382,7 +25385,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -25432,7 +25435,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -25482,7 +25485,7 @@
         <v>0</v>
       </c>
       <c r="P461" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25532,7 +25535,7 @@
         <v>0</v>
       </c>
       <c r="P462" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25582,7 +25585,7 @@
         <v>0</v>
       </c>
       <c r="P463" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25632,7 +25635,7 @@
         <v>0</v>
       </c>
       <c r="P464" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25932,7 +25935,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25982,7 +25985,7 @@
         <v>0</v>
       </c>
       <c r="P471" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -26032,7 +26035,7 @@
         <v>0</v>
       </c>
       <c r="P472" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -26082,7 +26085,7 @@
         <v>0</v>
       </c>
       <c r="P473" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -26132,7 +26135,7 @@
         <v>0</v>
       </c>
       <c r="P474" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -26182,7 +26185,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26232,7 +26235,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26282,7 +26285,7 @@
         <v>0</v>
       </c>
       <c r="P477" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26332,7 +26335,7 @@
         <v>0</v>
       </c>
       <c r="P478" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26382,7 +26385,7 @@
         <v>0</v>
       </c>
       <c r="P479" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26632,7 +26635,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26682,7 +26685,7 @@
         <v>0</v>
       </c>
       <c r="P485" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26732,7 +26735,7 @@
         <v>0</v>
       </c>
       <c r="P486" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26782,7 +26785,7 @@
         <v>0</v>
       </c>
       <c r="P487" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26832,7 +26835,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26882,7 +26885,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26932,7 +26935,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26982,7 +26985,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -27032,7 +27035,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27082,7 +27085,7 @@
         <v>0</v>
       </c>
       <c r="P493" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27132,7 +27135,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27182,7 +27185,7 @@
         <v>0</v>
       </c>
       <c r="P495" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27382,7 +27385,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27432,7 +27435,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27482,7 +27485,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27532,7 +27535,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27582,7 +27585,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27632,7 +27635,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27682,7 +27685,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27732,7 +27735,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27782,7 +27785,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27832,7 +27835,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27882,7 +27885,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27932,7 +27935,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27982,7 +27985,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28032,7 +28035,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28082,7 +28085,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28132,7 +28135,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28182,7 +28185,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28232,7 +28235,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28282,7 +28285,7 @@
         <v>0</v>
       </c>
       <c r="P517" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28311,7 +28314,7 @@
         <v>5.37</v>
       </c>
       <c r="P518" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28340,7 +28343,7 @@
         <v>5.6</v>
       </c>
       <c r="P519" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -28390,7 +28393,7 @@
         <v>0</v>
       </c>
       <c r="P520" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28440,7 +28443,7 @@
         <v>0</v>
       </c>
       <c r="P521" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28469,7 +28472,7 @@
         <v>5.37</v>
       </c>
       <c r="P522" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28498,7 +28501,7 @@
         <v>5.6</v>
       </c>
       <c r="P523" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28527,7 +28530,7 @@
         <v>5.77</v>
       </c>
       <c r="P524" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28577,7 +28580,7 @@
         <v>0</v>
       </c>
       <c r="P525" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28627,7 +28630,7 @@
         <v>0</v>
       </c>
       <c r="P526" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28677,7 +28680,7 @@
         <v>0</v>
       </c>
       <c r="P527" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28727,7 +28730,7 @@
         <v>0</v>
       </c>
       <c r="P528" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28777,7 +28780,7 @@
         <v>0</v>
       </c>
       <c r="P529" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28827,7 +28830,7 @@
         <v>0</v>
       </c>
       <c r="P530" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29027,7 +29030,7 @@
         <v>0</v>
       </c>
       <c r="P534" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29077,7 +29080,7 @@
         <v>0</v>
       </c>
       <c r="P535" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29127,7 +29130,7 @@
         <v>0</v>
       </c>
       <c r="P536" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29177,7 +29180,7 @@
         <v>0</v>
       </c>
       <c r="P537" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29227,7 +29230,7 @@
         <v>0</v>
       </c>
       <c r="P538" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29277,7 +29280,7 @@
         <v>0</v>
       </c>
       <c r="P539" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29327,7 +29330,7 @@
         <v>0</v>
       </c>
       <c r="P540" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29377,7 +29380,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29427,7 +29430,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29477,7 +29480,7 @@
         <v>0</v>
       </c>
       <c r="P543" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29527,7 +29530,7 @@
         <v>0</v>
       </c>
       <c r="P544" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29577,7 +29580,7 @@
         <v>0</v>
       </c>
       <c r="P545" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29627,7 +29630,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29677,7 +29680,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29727,7 +29730,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29777,7 +29780,7 @@
         <v>0</v>
       </c>
       <c r="P549" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29827,7 +29830,7 @@
         <v>0</v>
       </c>
       <c r="P550" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29877,7 +29880,7 @@
         <v>0</v>
       </c>
       <c r="P551" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29906,7 +29909,7 @@
         <v>6.55</v>
       </c>
       <c r="P552" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29935,7 +29938,7 @@
         <v>6.7</v>
       </c>
       <c r="P553" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29985,7 +29988,7 @@
         <v>0</v>
       </c>
       <c r="P554" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30035,7 +30038,7 @@
         <v>0</v>
       </c>
       <c r="P555" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30085,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="P556" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30135,7 +30138,7 @@
         <v>0</v>
       </c>
       <c r="P557" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30185,7 +30188,7 @@
         <v>0</v>
       </c>
       <c r="P558" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30285,7 +30288,7 @@
         <v>0</v>
       </c>
       <c r="P560" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30335,7 +30338,7 @@
         <v>0</v>
       </c>
       <c r="P561" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30385,7 +30388,7 @@
         <v>0</v>
       </c>
       <c r="P562" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30535,7 +30538,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30585,7 +30588,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30635,7 +30638,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30685,7 +30688,7 @@
         <v>0</v>
       </c>
       <c r="P568" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30735,7 +30738,7 @@
         <v>0</v>
       </c>
       <c r="P569" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30785,7 +30788,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30835,7 +30838,7 @@
         <v>0</v>
       </c>
       <c r="P571" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30885,7 +30888,7 @@
         <v>0</v>
       </c>
       <c r="P572" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30935,7 +30938,7 @@
         <v>0</v>
       </c>
       <c r="P573" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30985,7 +30988,7 @@
         <v>0</v>
       </c>
       <c r="P574" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31085,7 +31088,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31135,7 +31138,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31185,7 +31188,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31235,7 +31238,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31285,7 +31288,7 @@
         <v>0</v>
       </c>
       <c r="P580" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31335,7 +31338,7 @@
         <v>0</v>
       </c>
       <c r="P581" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31385,7 +31388,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31435,7 +31438,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31485,7 +31488,7 @@
         <v>0</v>
       </c>
       <c r="P584" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31535,7 +31538,7 @@
         <v>0</v>
       </c>
       <c r="P585" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31585,7 +31588,7 @@
         <v>0</v>
       </c>
       <c r="P586" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31635,7 +31638,7 @@
         <v>0</v>
       </c>
       <c r="P587" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31685,7 +31688,7 @@
         <v>0</v>
       </c>
       <c r="P588" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31735,7 +31738,7 @@
         <v>0</v>
       </c>
       <c r="P589" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31785,7 +31788,7 @@
         <v>0</v>
       </c>
       <c r="P590" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31835,7 +31838,7 @@
         <v>0</v>
       </c>
       <c r="P591" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31885,7 +31888,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31935,7 +31938,7 @@
         <v>0</v>
       </c>
       <c r="P593" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31985,7 +31988,7 @@
         <v>0</v>
       </c>
       <c r="P594" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32035,7 +32038,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32085,7 +32088,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32135,7 +32138,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32185,7 +32188,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32235,7 +32238,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32285,7 +32288,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32335,7 +32338,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32385,7 +32388,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32435,7 +32438,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32485,7 +32488,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32535,7 +32538,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32585,7 +32588,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32635,7 +32638,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32685,7 +32688,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32735,7 +32738,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32785,7 +32788,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32835,7 +32838,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32885,7 +32888,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32935,7 +32938,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33735,7 +33738,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33785,7 +33788,7 @@
         <v>0</v>
       </c>
       <c r="P630" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33835,7 +33838,7 @@
         <v>0</v>
       </c>
       <c r="P631" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33885,7 +33888,7 @@
         <v>0</v>
       </c>
       <c r="P632" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33935,7 +33938,7 @@
         <v>0</v>
       </c>
       <c r="P633" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33985,7 +33988,7 @@
         <v>0</v>
       </c>
       <c r="P634" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -34035,7 +34038,7 @@
         <v>0</v>
       </c>
       <c r="P635" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34085,7 +34088,7 @@
         <v>0</v>
       </c>
       <c r="P636" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34135,7 +34138,7 @@
         <v>0</v>
       </c>
       <c r="P637" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34185,7 +34188,7 @@
         <v>0</v>
       </c>
       <c r="P638" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34235,7 +34238,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34285,7 +34288,7 @@
         <v>0</v>
       </c>
       <c r="P640" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34335,7 +34338,7 @@
         <v>0</v>
       </c>
       <c r="P641" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34385,7 +34388,7 @@
         <v>0</v>
       </c>
       <c r="P642" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34435,7 +34438,7 @@
         <v>0</v>
       </c>
       <c r="P643" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34485,7 +34488,7 @@
         <v>0</v>
       </c>
       <c r="P644" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34535,7 +34538,7 @@
         <v>0</v>
       </c>
       <c r="P645" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34585,7 +34588,7 @@
         <v>0</v>
       </c>
       <c r="P646" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34635,7 +34638,7 @@
         <v>0</v>
       </c>
       <c r="P647" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34685,7 +34688,7 @@
         <v>0</v>
       </c>
       <c r="P648" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34735,7 +34738,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34785,7 +34788,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34835,7 +34838,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35035,7 +35038,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35085,7 +35088,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35135,7 +35138,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35285,7 +35288,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35335,7 +35338,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35435,7 +35438,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35535,7 +35538,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35585,7 +35588,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35614,7 +35617,7 @@
         <v>6.64</v>
       </c>
       <c r="P667" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35664,7 +35667,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35714,7 +35717,7 @@
         <v>0</v>
       </c>
       <c r="P669" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35764,7 +35767,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35814,7 +35817,7 @@
         <v>0</v>
       </c>
       <c r="P671" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35864,7 +35867,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35893,7 +35896,7 @@
         <v>6.64</v>
       </c>
       <c r="P673" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35922,7 +35925,7 @@
         <v>6.38</v>
       </c>
       <c r="P674" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35972,7 +35975,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36022,7 +36025,7 @@
         <v>0</v>
       </c>
       <c r="P676" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36072,7 +36075,7 @@
         <v>0</v>
       </c>
       <c r="P677" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36122,7 +36125,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36172,7 +36175,7 @@
         <v>0</v>
       </c>
       <c r="P679" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36222,7 +36225,7 @@
         <v>0</v>
       </c>
       <c r="P680" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36272,7 +36275,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36322,7 +36325,7 @@
         <v>0</v>
       </c>
       <c r="P682" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36372,7 +36375,7 @@
         <v>0</v>
       </c>
       <c r="P683" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36422,7 +36425,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36451,7 +36454,7 @@
         <v>6.64</v>
       </c>
       <c r="P685" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36480,7 +36483,7 @@
         <v>6.38</v>
       </c>
       <c r="P686" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36509,7 +36512,7 @@
         <v>6.21</v>
       </c>
       <c r="P687" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36559,7 +36562,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36609,7 +36612,7 @@
         <v>0</v>
       </c>
       <c r="P689" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36659,7 +36662,7 @@
         <v>0</v>
       </c>
       <c r="P690" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36709,7 +36712,7 @@
         <v>0</v>
       </c>
       <c r="P691" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36759,7 +36762,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36809,7 +36812,7 @@
         <v>0</v>
       </c>
       <c r="P693" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36859,7 +36862,7 @@
         <v>0</v>
       </c>
       <c r="P694" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36909,7 +36912,7 @@
         <v>0</v>
       </c>
       <c r="P695" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36959,7 +36962,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37009,7 +37012,7 @@
         <v>0</v>
       </c>
       <c r="P697" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37059,7 +37062,7 @@
         <v>0</v>
       </c>
       <c r="P698" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37109,7 +37112,7 @@
         <v>0</v>
       </c>
       <c r="P699" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37159,7 +37162,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -37209,7 +37212,7 @@
         <v>0</v>
       </c>
       <c r="P701" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37259,7 +37262,7 @@
         <v>0</v>
       </c>
       <c r="P702" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37309,7 +37312,7 @@
         <v>0</v>
       </c>
       <c r="P703" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37359,7 +37362,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37409,7 +37412,7 @@
         <v>0</v>
       </c>
       <c r="P705" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37459,7 +37462,7 @@
         <v>0</v>
       </c>
       <c r="P706" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37509,7 +37512,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37559,7 +37562,7 @@
         <v>0</v>
       </c>
       <c r="P708" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37609,7 +37612,7 @@
         <v>0</v>
       </c>
       <c r="P709" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37659,7 +37662,7 @@
         <v>0</v>
       </c>
       <c r="P710" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37709,7 +37712,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37759,7 +37762,7 @@
         <v>0</v>
       </c>
       <c r="P712" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37809,7 +37812,7 @@
         <v>0</v>
       </c>
       <c r="P713" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37859,7 +37862,7 @@
         <v>0</v>
       </c>
       <c r="P714" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37909,7 +37912,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37959,7 +37962,7 @@
         <v>0</v>
       </c>
       <c r="P716" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38009,7 +38012,7 @@
         <v>0</v>
       </c>
       <c r="P717" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38059,7 +38062,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -38109,7 +38112,7 @@
         <v>0</v>
       </c>
       <c r="P719" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38159,7 +38162,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38209,7 +38212,7 @@
         <v>0</v>
       </c>
       <c r="P721" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38259,7 +38262,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38309,7 +38312,7 @@
         <v>0</v>
       </c>
       <c r="P723" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38359,7 +38362,7 @@
         <v>0</v>
       </c>
       <c r="P724" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38409,7 +38412,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38459,7 +38462,7 @@
         <v>0</v>
       </c>
       <c r="P726" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38509,7 +38512,7 @@
         <v>0</v>
       </c>
       <c r="P727" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38559,7 +38562,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38588,7 +38591,7 @@
         <v>6.3</v>
       </c>
       <c r="P729" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38617,7 +38620,7 @@
         <v>6.17</v>
       </c>
       <c r="P730" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38817,7 +38820,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38867,7 +38870,7 @@
         <v>0</v>
       </c>
       <c r="P735" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38917,7 +38920,7 @@
         <v>0</v>
       </c>
       <c r="P736" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38967,7 +38970,7 @@
         <v>0</v>
       </c>
       <c r="P737" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -39367,7 +39370,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39417,7 +39420,7 @@
         <v>0</v>
       </c>
       <c r="P746" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39467,7 +39470,7 @@
         <v>0</v>
       </c>
       <c r="P747" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39517,7 +39520,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39567,7 +39570,7 @@
         <v>0</v>
       </c>
       <c r="P749" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39617,7 +39620,7 @@
         <v>0</v>
       </c>
       <c r="P750" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39667,7 +39670,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39717,7 +39720,7 @@
         <v>0</v>
       </c>
       <c r="P752" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39767,7 +39770,7 @@
         <v>0</v>
       </c>
       <c r="P753" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39817,7 +39820,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39867,7 +39870,7 @@
         <v>0</v>
       </c>
       <c r="P755" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39917,7 +39920,7 @@
         <v>0</v>
       </c>
       <c r="P756" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39967,7 +39970,7 @@
         <v>0</v>
       </c>
       <c r="P757" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40017,7 +40020,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40067,7 +40070,7 @@
         <v>0</v>
       </c>
       <c r="P759" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40117,7 +40120,7 @@
         <v>0</v>
       </c>
       <c r="P760" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40167,7 +40170,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40217,7 +40220,7 @@
         <v>0</v>
       </c>
       <c r="P762" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40267,7 +40270,7 @@
         <v>0</v>
       </c>
       <c r="P763" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40317,7 +40320,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40367,7 +40370,7 @@
         <v>0</v>
       </c>
       <c r="P765" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40417,7 +40420,7 @@
         <v>0</v>
       </c>
       <c r="P766" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40467,7 +40470,7 @@
         <v>0</v>
       </c>
       <c r="P767" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40517,7 +40520,7 @@
         <v>0</v>
       </c>
       <c r="P768" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40567,7 +40570,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40617,7 +40620,7 @@
         <v>0</v>
       </c>
       <c r="P770" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40667,7 +40670,7 @@
         <v>0</v>
       </c>
       <c r="P771" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40717,7 +40720,7 @@
         <v>0</v>
       </c>
       <c r="P772" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40767,7 +40770,7 @@
         <v>0</v>
       </c>
       <c r="P773" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40817,7 +40820,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40867,7 +40870,7 @@
         <v>0</v>
       </c>
       <c r="P775" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40917,7 +40920,7 @@
         <v>0</v>
       </c>
       <c r="P776" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40967,7 +40970,7 @@
         <v>0</v>
       </c>
       <c r="P777" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -41017,7 +41020,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41067,7 +41070,7 @@
         <v>0</v>
       </c>
       <c r="P779" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41117,7 +41120,7 @@
         <v>0</v>
       </c>
       <c r="P780" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41167,7 +41170,7 @@
         <v>0</v>
       </c>
       <c r="P781" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41217,7 +41220,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41267,7 +41270,7 @@
         <v>0</v>
       </c>
       <c r="P783" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41317,7 +41320,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41367,7 +41370,7 @@
         <v>0</v>
       </c>
       <c r="P785" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41417,7 +41420,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41467,7 +41470,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41517,7 +41520,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41567,7 +41570,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41617,7 +41620,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41667,7 +41670,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41717,7 +41720,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41767,7 +41770,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41817,7 +41820,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41867,7 +41870,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41917,7 +41920,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41967,7 +41970,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -42017,7 +42020,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42067,7 +42070,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42117,7 +42120,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42167,7 +42170,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42217,7 +42220,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42267,7 +42270,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42317,7 +42320,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42367,7 +42370,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42417,7 +42420,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42467,7 +42470,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42517,7 +42520,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42567,7 +42570,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42617,7 +42620,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42667,7 +42670,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42717,7 +42720,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42917,7 +42920,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42967,7 +42970,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43017,7 +43020,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -43067,7 +43070,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -43117,7 +43120,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43167,7 +43170,7 @@
         <v>0</v>
       </c>
       <c r="P821" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43217,7 +43220,7 @@
         <v>0</v>
       </c>
       <c r="P822" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43667,7 +43670,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43717,7 +43720,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43767,7 +43770,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43817,7 +43820,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43846,7 +43849,7 @@
         <v>5.63</v>
       </c>
       <c r="P835" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43896,7 +43899,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43946,7 +43949,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43996,7 +43999,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44046,7 +44049,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44096,7 +44099,7 @@
         <v>0</v>
       </c>
       <c r="P840" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44296,7 +44299,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44346,7 +44349,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44396,7 +44399,7 @@
         <v>0</v>
       </c>
       <c r="P846" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44446,7 +44449,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44496,7 +44499,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44546,7 +44549,7 @@
         <v>0</v>
       </c>
       <c r="P849" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44596,7 +44599,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44646,7 +44649,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44696,7 +44699,7 @@
         <v>0</v>
       </c>
       <c r="P852" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44746,7 +44749,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44796,7 +44799,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44846,7 +44849,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44896,7 +44899,7 @@
         <v>0</v>
       </c>
       <c r="P856" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44946,7 +44949,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44996,7 +44999,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45046,7 +45049,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45096,7 +45099,7 @@
         <v>0</v>
       </c>
       <c r="P860" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45296,7 +45299,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45346,7 +45349,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45396,7 +45399,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45446,7 +45449,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45496,7 +45499,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45546,7 +45549,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45596,7 +45599,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45646,7 +45649,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45696,7 +45699,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45746,7 +45749,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45796,7 +45799,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45846,7 +45849,7 @@
         <v>0</v>
       </c>
       <c r="P875" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45896,7 +45899,7 @@
         <v>0</v>
       </c>
       <c r="P876" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45946,7 +45949,7 @@
         <v>0</v>
       </c>
       <c r="P877" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46096,7 +46099,7 @@
         <v>0</v>
       </c>
       <c r="P880" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46146,7 +46149,7 @@
         <v>0</v>
       </c>
       <c r="P881" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46196,7 +46199,7 @@
         <v>0</v>
       </c>
       <c r="P882" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46246,7 +46249,7 @@
         <v>0</v>
       </c>
       <c r="P883" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46296,7 +46299,7 @@
         <v>0</v>
       </c>
       <c r="P884" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46325,7 +46328,7 @@
         <v>5.6</v>
       </c>
       <c r="P885" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46375,7 +46378,7 @@
         <v>0</v>
       </c>
       <c r="P886" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46575,7 +46578,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46625,7 +46628,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46675,7 +46678,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46725,7 +46728,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46775,7 +46778,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46825,7 +46828,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46875,7 +46878,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -46925,7 +46928,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -46975,7 +46978,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47025,7 +47028,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47075,7 +47078,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47125,7 +47128,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47275,7 +47278,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47325,7 +47328,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47375,7 +47378,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47425,7 +47428,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47475,7 +47478,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47525,7 +47528,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47575,7 +47578,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47625,7 +47628,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47675,7 +47678,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47725,7 +47728,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47775,7 +47778,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47825,7 +47828,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47875,7 +47878,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -47925,7 +47928,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47975,7 +47978,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48025,7 +48028,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48075,7 +48078,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48125,7 +48128,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48175,7 +48178,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48225,7 +48228,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48275,7 +48278,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48325,7 +48328,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48375,7 +48378,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48425,7 +48428,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48475,7 +48478,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48525,7 +48528,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48575,7 +48578,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48625,7 +48628,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48675,7 +48678,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48725,7 +48728,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48775,7 +48778,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48825,7 +48828,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48875,7 +48878,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48925,7 +48928,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48975,7 +48978,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49025,7 +49028,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49075,7 +49078,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49125,7 +49128,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49175,7 +49178,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49225,7 +49228,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49275,7 +49278,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49325,7 +49328,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49375,7 +49378,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49425,7 +49428,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49475,7 +49478,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49525,7 +49528,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49575,7 +49578,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49625,7 +49628,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49675,7 +49678,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49725,7 +49728,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49775,7 +49778,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49825,7 +49828,7 @@
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49875,7 +49878,7 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="957" spans="1:16">
@@ -49925,7 +49928,7 @@
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="958" spans="1:16">
@@ -49975,7 +49978,7 @@
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="959" spans="1:16">
@@ -50025,7 +50028,7 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="960" spans="1:16">
@@ -50075,7 +50078,7 @@
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="961" spans="1:16">
@@ -50125,7 +50128,7 @@
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="962" spans="1:16">
@@ -50175,51 +50178,51 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="963" spans="1:16">
       <c r="A963" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B963" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="C963">
-        <v>2.047715219225316</v>
+        <v>3.120086387124764</v>
       </c>
       <c r="D963" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E963">
-        <v>2.769139254491011</v>
+        <v>2.483561200741584</v>
       </c>
       <c r="F963">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G963">
-        <v>0.009132284780774682</v>
+        <v>0.009259913612875236</v>
       </c>
       <c r="H963">
-        <v>0.009110860745508988</v>
+        <v>0.008796438799258417</v>
       </c>
       <c r="I963">
-        <v>0.7214240352656947</v>
+        <v>0.6365251863831807</v>
       </c>
       <c r="J963">
-        <v>0.06878222875290647</v>
+        <v>0.06922014910654421</v>
       </c>
       <c r="K963">
-        <v>51.5</v>
+        <v>44.35</v>
       </c>
       <c r="L963">
-        <v>5.59</v>
+        <v>6.19</v>
       </c>
       <c r="M963">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N963">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O963">
         <v>1</v>
@@ -50230,96 +50233,96 @@
     </row>
     <row r="964" spans="1:16">
       <c r="A964" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B964" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="C964">
-        <v>3.235589072759032</v>
+        <v>2.047715219225316</v>
       </c>
       <c r="D964" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="E964">
-        <v>2.503530368867464</v>
+        <v>2.769139254491011</v>
       </c>
       <c r="F964">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G964">
-        <v>0.00872441092724097</v>
+        <v>0.009132284780774682</v>
       </c>
       <c r="H964">
-        <v>0.008776469631132535</v>
+        <v>0.009110860745508988</v>
       </c>
       <c r="I964">
-        <v>0.732058703891568</v>
+        <v>0.7214240352656947</v>
       </c>
       <c r="J964">
         <v>0.06878222875290647</v>
       </c>
       <c r="K964">
-        <v>39.9</v>
+        <v>51.5</v>
       </c>
       <c r="L964">
-        <v>5.98</v>
+        <v>5.59</v>
       </c>
       <c r="M964">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="N964">
-        <v>5.64</v>
+        <v>5.94</v>
       </c>
       <c r="O964">
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="965" spans="1:16">
       <c r="A965" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B965" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C965">
-        <v>6.518598702106193</v>
+        <v>3.235589072759032</v>
       </c>
       <c r="D965" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E965">
-        <v>6.052303309796228</v>
+        <v>2.503530368867464</v>
       </c>
       <c r="F965">
         <v>-1</v>
       </c>
       <c r="G965">
-        <v>0.005861401297893808</v>
+        <v>0.00872441092724097</v>
       </c>
       <c r="H965">
-        <v>0.005387696690203772</v>
+        <v>0.008776469631132535</v>
       </c>
       <c r="I965">
-        <v>0.4662953923099646</v>
+        <v>0.732058703891568</v>
       </c>
       <c r="J965">
-        <v>-0.007409215380071977</v>
+        <v>0.06878222875290647</v>
       </c>
       <c r="K965">
-        <v>44.35</v>
+        <v>39.9</v>
       </c>
       <c r="L965">
-        <v>6.19</v>
+        <v>5.98</v>
       </c>
       <c r="M965">
-        <v>44.85</v>
+        <v>45.6</v>
       </c>
       <c r="N965">
-        <v>5.72</v>
+        <v>5.64</v>
       </c>
       <c r="O965">
         <v>1</v>
@@ -50330,49 +50333,49 @@
     </row>
     <row r="966" spans="1:16">
       <c r="A966" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B966" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C966">
-        <v>5.686375937492171</v>
+        <v>3.139508154808598</v>
       </c>
       <c r="D966" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E966">
-        <v>5.745635015954163</v>
+        <v>2.503530368867464</v>
       </c>
       <c r="F966">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G966">
-        <v>0.00503362406250783</v>
+        <v>0.009240491845191403</v>
       </c>
       <c r="H966">
-        <v>0.005094364984045837</v>
+        <v>0.008776469631132535</v>
       </c>
       <c r="I966">
-        <v>0.05925907846199241</v>
+        <v>0.635977785941134</v>
       </c>
       <c r="J966">
-        <v>-0.007409215380071977</v>
+        <v>0.06878222875290647</v>
       </c>
       <c r="K966">
-        <v>44.05</v>
+        <v>44.35</v>
       </c>
       <c r="L966">
-        <v>5.36</v>
+        <v>6.19</v>
       </c>
       <c r="M966">
-        <v>43.95</v>
+        <v>45.6</v>
       </c>
       <c r="N966">
-        <v>5.42</v>
+        <v>5.64</v>
       </c>
       <c r="O966">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P966" t="s">
         <v>789</v>
@@ -50386,28 +50389,28 @@
         <v>221</v>
       </c>
       <c r="C967">
-        <v>6.991566556621656</v>
+        <v>6.518598702106193</v>
       </c>
       <c r="D967" t="s">
         <v>462</v>
       </c>
       <c r="E967">
-        <v>6.530603383641066</v>
+        <v>6.052303309796228</v>
       </c>
       <c r="F967">
         <v>-1</v>
       </c>
       <c r="G967">
-        <v>0.005388433443378345</v>
+        <v>0.005861401297893808</v>
       </c>
       <c r="H967">
-        <v>0.004909396616358934</v>
+        <v>0.005387696690203772</v>
       </c>
       <c r="I967">
-        <v>0.4609631729805903</v>
+        <v>0.4662953923099646</v>
       </c>
       <c r="J967">
-        <v>-0.01807365403881975</v>
+        <v>-0.007409215380071977</v>
       </c>
       <c r="K967">
         <v>44.35</v>
@@ -50436,40 +50439,40 @@
         <v>222</v>
       </c>
       <c r="C968">
-        <v>6.15614446041001</v>
+        <v>5.568223359810994</v>
       </c>
       <c r="D968" t="s">
         <v>463</v>
       </c>
       <c r="E968">
-        <v>6.214337095006128</v>
+        <v>5.631927967501031</v>
       </c>
       <c r="F968">
         <v>1</v>
       </c>
       <c r="G968">
-        <v>0.004563855539589991</v>
+        <v>0.004951776640189006</v>
       </c>
       <c r="H968">
-        <v>0.004625662904993872</v>
+        <v>0.00500807203249897</v>
       </c>
       <c r="I968">
-        <v>0.0581926345961179</v>
+        <v>0.0637046076900365</v>
       </c>
       <c r="J968">
-        <v>-0.01807365403881975</v>
+        <v>-0.007409215380071977</v>
       </c>
       <c r="K968">
-        <v>44.05</v>
+        <v>41.6</v>
       </c>
       <c r="L968">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="M968">
-        <v>43.95</v>
+        <v>42.1</v>
       </c>
       <c r="N968">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="O968">
         <v>0</v>
@@ -50486,28 +50489,28 @@
         <v>221</v>
       </c>
       <c r="C969">
-        <v>7.158772656458988</v>
+        <v>6.991566556621656</v>
       </c>
       <c r="D969" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E969">
-        <v>6.699694557884682</v>
+        <v>6.426382421524607</v>
       </c>
       <c r="F969">
         <v>-1</v>
       </c>
       <c r="G969">
-        <v>0.005221227343541013</v>
+        <v>0.005388433443378345</v>
       </c>
       <c r="H969">
-        <v>0.004740305442115318</v>
+        <v>0.004913617578475394</v>
       </c>
       <c r="I969">
-        <v>0.4590780985743068</v>
+        <v>0.5651841350970495</v>
       </c>
       <c r="J969">
-        <v>-0.02184380285138643</v>
+        <v>-0.01807365403881975</v>
       </c>
       <c r="K969">
         <v>44.35</v>
@@ -50516,10 +50519,10 @@
         <v>6.19</v>
       </c>
       <c r="M969">
-        <v>44.85</v>
+        <v>41.85</v>
       </c>
       <c r="N969">
-        <v>5.72</v>
+        <v>5.67</v>
       </c>
       <c r="O969">
         <v>1</v>
@@ -50536,40 +50539,40 @@
         <v>222</v>
       </c>
       <c r="C970">
-        <v>6.322219515603573</v>
+        <v>6.011864008014902</v>
       </c>
       <c r="D970" t="s">
         <v>463</v>
       </c>
       <c r="E970">
-        <v>6.380035135318433</v>
+        <v>6.080900835034312</v>
       </c>
       <c r="F970">
         <v>1</v>
       </c>
       <c r="G970">
-        <v>0.004397780484396428</v>
+        <v>0.004508135991985098</v>
       </c>
       <c r="H970">
-        <v>0.004459964864681567</v>
+        <v>0.004559099164965689</v>
       </c>
       <c r="I970">
-        <v>0.05781561971486049</v>
+        <v>0.06903682701940994</v>
       </c>
       <c r="J970">
-        <v>-0.02184380285138643</v>
+        <v>-0.01807365403881975</v>
       </c>
       <c r="K970">
-        <v>44.05</v>
+        <v>41.6</v>
       </c>
       <c r="L970">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="M970">
-        <v>43.95</v>
+        <v>42.1</v>
       </c>
       <c r="N970">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="O970">
         <v>0</v>
@@ -50583,99 +50586,249 @@
         <v>0</v>
       </c>
       <c r="B971" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C971">
-        <v>6.34308163058533</v>
+        <v>7.158772656458988</v>
       </c>
       <c r="D971" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E971">
-        <v>6.400849890220778</v>
+        <v>6.584163149330522</v>
       </c>
       <c r="F971">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G971">
-        <v>0.00437691836941467</v>
+        <v>0.005221227343541013</v>
       </c>
       <c r="H971">
-        <v>0.004439150109779222</v>
+        <v>0.004755836850669478</v>
       </c>
       <c r="I971">
-        <v>0.05776825963544763</v>
+        <v>0.574609507128466</v>
       </c>
       <c r="J971">
-        <v>-0.02231740364552396</v>
+        <v>-0.02184380285138643</v>
       </c>
       <c r="K971">
-        <v>44.05</v>
+        <v>44.35</v>
       </c>
       <c r="L971">
-        <v>5.36</v>
+        <v>6.19</v>
       </c>
       <c r="M971">
-        <v>43.95</v>
+        <v>41.85</v>
       </c>
       <c r="N971">
-        <v>5.42</v>
+        <v>5.67</v>
       </c>
       <c r="O971">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P971" t="s">
-        <v>221</v>
+        <v>792</v>
       </c>
     </row>
     <row r="972" spans="1:16">
       <c r="A972" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B972" t="s">
         <v>222</v>
       </c>
       <c r="C972">
-        <v>6.311554267650159</v>
+        <v>6.168702198617676</v>
       </c>
       <c r="D972" t="s">
         <v>463</v>
       </c>
       <c r="E972">
-        <v>6.369394099051633</v>
+        <v>6.239624100043369</v>
       </c>
       <c r="F972">
         <v>1</v>
       </c>
       <c r="G972">
-        <v>0.004408445732349842</v>
+        <v>0.004351297801382324</v>
       </c>
       <c r="H972">
-        <v>0.004470605900948367</v>
+        <v>0.004400375899956632</v>
       </c>
       <c r="I972">
-        <v>0.05783983140147431</v>
+        <v>0.07092190142569343</v>
       </c>
       <c r="J972">
-        <v>-0.02160168598524764</v>
+        <v>-0.02184380285138643</v>
       </c>
       <c r="K972">
-        <v>44.05</v>
+        <v>41.6</v>
       </c>
       <c r="L972">
-        <v>5.36</v>
+        <v>5.26</v>
       </c>
       <c r="M972">
-        <v>43.95</v>
+        <v>42.1</v>
       </c>
       <c r="N972">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="O972">
         <v>0</v>
       </c>
       <c r="P972" t="s">
         <v>792</v>
+      </c>
+    </row>
+    <row r="973" spans="1:16">
+      <c r="A973" s="1">
+        <v>0</v>
+      </c>
+      <c r="B973" t="s">
+        <v>222</v>
+      </c>
+      <c r="C973">
+        <v>6.188403991653797</v>
+      </c>
+      <c r="D973" t="s">
+        <v>463</v>
+      </c>
+      <c r="E973">
+        <v>6.259562693476559</v>
+      </c>
+      <c r="F973">
+        <v>1</v>
+      </c>
+      <c r="G973">
+        <v>0.004331596008346203</v>
+      </c>
+      <c r="H973">
+        <v>0.004380437306523442</v>
+      </c>
+      <c r="I973">
+        <v>0.07115870182276218</v>
+      </c>
+      <c r="J973">
+        <v>-0.02231740364552396</v>
+      </c>
+      <c r="K973">
+        <v>41.6</v>
+      </c>
+      <c r="L973">
+        <v>5.26</v>
+      </c>
+      <c r="M973">
+        <v>42.1</v>
+      </c>
+      <c r="N973">
+        <v>5.32</v>
+      </c>
+      <c r="O973">
+        <v>0</v>
+      </c>
+      <c r="P973" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="974" spans="1:16">
+      <c r="A974" s="1">
+        <v>0</v>
+      </c>
+      <c r="B974" t="s">
+        <v>222</v>
+      </c>
+      <c r="C974">
+        <v>6.158630136986302</v>
+      </c>
+      <c r="D974" t="s">
+        <v>463</v>
+      </c>
+      <c r="E974">
+        <v>6.229430979978925</v>
+      </c>
+      <c r="F974">
+        <v>1</v>
+      </c>
+      <c r="G974">
+        <v>0.004361369863013698</v>
+      </c>
+      <c r="H974">
+        <v>0.004410569020021076</v>
+      </c>
+      <c r="I974">
+        <v>0.07080084299262346</v>
+      </c>
+      <c r="J974">
+        <v>-0.02160168598524764</v>
+      </c>
+      <c r="K974">
+        <v>41.6</v>
+      </c>
+      <c r="L974">
+        <v>5.26</v>
+      </c>
+      <c r="M974">
+        <v>42.1</v>
+      </c>
+      <c r="N974">
+        <v>5.32</v>
+      </c>
+      <c r="O974">
+        <v>0</v>
+      </c>
+      <c r="P974" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="975" spans="1:16">
+      <c r="A975" s="1">
+        <v>0</v>
+      </c>
+      <c r="B975" t="s">
+        <v>222</v>
+      </c>
+      <c r="C975">
+        <v>5.32829599901169</v>
+      </c>
+      <c r="D975" t="s">
+        <v>463</v>
+      </c>
+      <c r="E975">
+        <v>5.389116864384427</v>
+      </c>
+      <c r="F975">
+        <v>1</v>
+      </c>
+      <c r="G975">
+        <v>0.005191704000988309</v>
+      </c>
+      <c r="H975">
+        <v>0.005250883135615574</v>
+      </c>
+      <c r="I975">
+        <v>0.06082086537273668</v>
+      </c>
+      <c r="J975">
+        <v>-0.00164173074547332</v>
+      </c>
+      <c r="K975">
+        <v>41.6</v>
+      </c>
+      <c r="L975">
+        <v>5.26</v>
+      </c>
+      <c r="M975">
+        <v>42.1</v>
+      </c>
+      <c r="N975">
+        <v>5.32</v>
+      </c>
+      <c r="O975">
+        <v>0</v>
+      </c>
+      <c r="P975" t="s">
+        <v>462</v>
       </c>
     </row>
   </sheetData>

--- a/s60_signal/position-2319-151-800.xlsx
+++ b/s60_signal/position-2319-151-800.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2906" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2920" uniqueCount="795">
   <si>
     <t>trade_time</t>
   </si>
@@ -1399,13 +1399,16 @@
     <t>2021-01-22</t>
   </si>
   <si>
+    <t>2021-05-26</t>
+  </si>
+  <si>
     <t>2021-01-28</t>
   </si>
   <si>
-    <t>2021-05-26</t>
-  </si>
-  <si>
     <t>2021-04-26</t>
+  </si>
+  <si>
+    <t>2021-08-03</t>
   </si>
   <si>
     <t>2010-03-04</t>
@@ -2753,7 +2756,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P976"/>
+  <dimension ref="A1:P980"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -2850,7 +2853,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:16">
@@ -2900,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="P3" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:16">
@@ -2950,7 +2953,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -3000,7 +3003,7 @@
         <v>0</v>
       </c>
       <c r="P5" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -3050,7 +3053,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -3100,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="P7" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -3150,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="P8" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:16">
@@ -3200,7 +3203,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:16">
@@ -3250,7 +3253,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:16">
@@ -3300,7 +3303,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:16">
@@ -3350,7 +3353,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="13" spans="1:16">
@@ -3400,7 +3403,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="14" spans="1:16">
@@ -3450,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="15" spans="1:16">
@@ -3500,7 +3503,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="16" spans="1:16">
@@ -3550,7 +3553,7 @@
         <v>0</v>
       </c>
       <c r="P16" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:16">
@@ -3600,7 +3603,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="18" spans="1:16">
@@ -3650,7 +3653,7 @@
         <v>1</v>
       </c>
       <c r="P18" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="19" spans="1:16">
@@ -3700,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:16">
@@ -3750,7 +3753,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="21" spans="1:16">
@@ -3800,7 +3803,7 @@
         <v>1</v>
       </c>
       <c r="P21" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="22" spans="1:16">
@@ -3850,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="P22" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="23" spans="1:16">
@@ -3900,7 +3903,7 @@
         <v>0</v>
       </c>
       <c r="P23" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="24" spans="1:16">
@@ -3950,7 +3953,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="25" spans="1:16">
@@ -4000,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="26" spans="1:16">
@@ -4050,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="P26" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="27" spans="1:16">
@@ -4100,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="P27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="28" spans="1:16">
@@ -4150,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="P28" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:16">
@@ -4200,7 +4203,7 @@
         <v>0</v>
       </c>
       <c r="P29" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="30" spans="1:16">
@@ -4250,7 +4253,7 @@
         <v>1</v>
       </c>
       <c r="P30" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="31" spans="1:16">
@@ -4300,7 +4303,7 @@
         <v>0</v>
       </c>
       <c r="P31" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="32" spans="1:16">
@@ -4350,7 +4353,7 @@
         <v>1</v>
       </c>
       <c r="P32" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="33" spans="1:16">
@@ -4400,7 +4403,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="34" spans="1:16">
@@ -4450,7 +4453,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="35" spans="1:16">
@@ -4500,7 +4503,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="36" spans="1:16">
@@ -4550,7 +4553,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="37" spans="1:16">
@@ -4600,7 +4603,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="38" spans="1:16">
@@ -4700,7 +4703,7 @@
         <v>1</v>
       </c>
       <c r="P39" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="40" spans="1:16">
@@ -4750,7 +4753,7 @@
         <v>1</v>
       </c>
       <c r="P40" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="41" spans="1:16">
@@ -4850,7 +4853,7 @@
         <v>1</v>
       </c>
       <c r="P42" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="43" spans="1:16">
@@ -4900,7 +4903,7 @@
         <v>1</v>
       </c>
       <c r="P43" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="44" spans="1:16">
@@ -4950,7 +4953,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="45" spans="1:16">
@@ -5000,7 +5003,7 @@
         <v>1</v>
       </c>
       <c r="P45" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="46" spans="1:16">
@@ -5050,7 +5053,7 @@
         <v>1</v>
       </c>
       <c r="P46" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="47" spans="1:16">
@@ -5100,7 +5103,7 @@
         <v>1</v>
       </c>
       <c r="P47" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="48" spans="1:16">
@@ -5150,7 +5153,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="49" spans="1:16">
@@ -5200,7 +5203,7 @@
         <v>1</v>
       </c>
       <c r="P49" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="50" spans="1:16">
@@ -5250,7 +5253,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" spans="1:16">
@@ -5300,7 +5303,7 @@
         <v>1</v>
       </c>
       <c r="P51" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="52" spans="1:16">
@@ -5350,7 +5353,7 @@
         <v>1</v>
       </c>
       <c r="P52" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="53" spans="1:16">
@@ -5400,7 +5403,7 @@
         <v>1</v>
       </c>
       <c r="P53" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="54" spans="1:16">
@@ -5450,7 +5453,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="55" spans="1:16">
@@ -5500,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="P55" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="56" spans="1:16">
@@ -5550,7 +5553,7 @@
         <v>1</v>
       </c>
       <c r="P56" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="57" spans="1:16">
@@ -5600,7 +5603,7 @@
         <v>1</v>
       </c>
       <c r="P57" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="58" spans="1:16">
@@ -5650,7 +5653,7 @@
         <v>1</v>
       </c>
       <c r="P58" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="59" spans="1:16">
@@ -5700,7 +5703,7 @@
         <v>1</v>
       </c>
       <c r="P59" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="60" spans="1:16">
@@ -5750,7 +5753,7 @@
         <v>1</v>
       </c>
       <c r="P60" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="61" spans="1:16">
@@ -5800,7 +5803,7 @@
         <v>1</v>
       </c>
       <c r="P61" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="62" spans="1:16">
@@ -5850,7 +5853,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="63" spans="1:16">
@@ -5900,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="P63" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="64" spans="1:16">
@@ -5950,7 +5953,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="65" spans="1:16">
@@ -6000,7 +6003,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="66" spans="1:16">
@@ -6050,7 +6053,7 @@
         <v>1</v>
       </c>
       <c r="P66" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="67" spans="1:16">
@@ -6100,7 +6103,7 @@
         <v>1</v>
       </c>
       <c r="P67" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="68" spans="1:16">
@@ -6150,7 +6153,7 @@
         <v>1</v>
       </c>
       <c r="P68" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="69" spans="1:16">
@@ -6200,7 +6203,7 @@
         <v>1</v>
       </c>
       <c r="P69" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="70" spans="1:16">
@@ -6250,7 +6253,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="71" spans="1:16">
@@ -6300,7 +6303,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="72" spans="1:16">
@@ -6350,7 +6353,7 @@
         <v>1</v>
       </c>
       <c r="P72" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="73" spans="1:16">
@@ -6400,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="P73" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="74" spans="1:16">
@@ -6450,7 +6453,7 @@
         <v>1</v>
       </c>
       <c r="P74" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="75" spans="1:16">
@@ -6500,7 +6503,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="76" spans="1:16">
@@ -6550,7 +6553,7 @@
         <v>1</v>
       </c>
       <c r="P76" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="77" spans="1:16">
@@ -6600,7 +6603,7 @@
         <v>1</v>
       </c>
       <c r="P77" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="78" spans="1:16">
@@ -6650,7 +6653,7 @@
         <v>1</v>
       </c>
       <c r="P78" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="79" spans="1:16">
@@ -6700,7 +6703,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="80" spans="1:16">
@@ -6750,7 +6753,7 @@
         <v>1</v>
       </c>
       <c r="P80" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="81" spans="1:16">
@@ -6800,7 +6803,7 @@
         <v>1</v>
       </c>
       <c r="P81" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="82" spans="1:16">
@@ -6850,7 +6853,7 @@
         <v>1</v>
       </c>
       <c r="P82" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="83" spans="1:16">
@@ -6900,7 +6903,7 @@
         <v>1</v>
       </c>
       <c r="P83" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="84" spans="1:16">
@@ -6950,7 +6953,7 @@
         <v>1</v>
       </c>
       <c r="P84" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="85" spans="1:16">
@@ -7000,7 +7003,7 @@
         <v>1</v>
       </c>
       <c r="P85" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="86" spans="1:16">
@@ -7050,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="87" spans="1:16">
@@ -7100,7 +7103,7 @@
         <v>1</v>
       </c>
       <c r="P87" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="88" spans="1:16">
@@ -7150,7 +7153,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="89" spans="1:16">
@@ -7350,7 +7353,7 @@
         <v>1</v>
       </c>
       <c r="P92" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="93" spans="1:16">
@@ -7400,7 +7403,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="94" spans="1:16">
@@ -7450,7 +7453,7 @@
         <v>1</v>
       </c>
       <c r="P94" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="95" spans="1:16">
@@ -7500,7 +7503,7 @@
         <v>1</v>
       </c>
       <c r="P95" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:16">
@@ -7550,7 +7553,7 @@
         <v>1</v>
       </c>
       <c r="P96" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="97" spans="1:16">
@@ -7600,7 +7603,7 @@
         <v>1</v>
       </c>
       <c r="P97" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="98" spans="1:16">
@@ -7650,7 +7653,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="99" spans="1:16">
@@ -7700,7 +7703,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="100" spans="1:16">
@@ -7750,7 +7753,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="101" spans="1:16">
@@ -7800,7 +7803,7 @@
         <v>1</v>
       </c>
       <c r="P101" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="102" spans="1:16">
@@ -7850,7 +7853,7 @@
         <v>1</v>
       </c>
       <c r="P102" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="103" spans="1:16">
@@ -7900,7 +7903,7 @@
         <v>1</v>
       </c>
       <c r="P103" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="104" spans="1:16">
@@ -7950,7 +7953,7 @@
         <v>1</v>
       </c>
       <c r="P104" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="105" spans="1:16">
@@ -8000,7 +8003,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="106" spans="1:16">
@@ -8050,7 +8053,7 @@
         <v>1</v>
       </c>
       <c r="P106" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="107" spans="1:16">
@@ -8100,7 +8103,7 @@
         <v>0</v>
       </c>
       <c r="P107" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="108" spans="1:16">
@@ -8150,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="P108" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="109" spans="1:16">
@@ -8200,7 +8203,7 @@
         <v>0</v>
       </c>
       <c r="P109" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="110" spans="1:16">
@@ -8250,7 +8253,7 @@
         <v>1</v>
       </c>
       <c r="P110" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="111" spans="1:16">
@@ -8279,7 +8282,7 @@
         <v>8</v>
       </c>
       <c r="P111" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="112" spans="1:16">
@@ -8308,7 +8311,7 @@
         <v>7.75</v>
       </c>
       <c r="P112" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="113" spans="1:16">
@@ -8337,7 +8340,7 @@
         <v>7.82</v>
       </c>
       <c r="P113" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="114" spans="1:16">
@@ -8387,7 +8390,7 @@
         <v>1</v>
       </c>
       <c r="P114" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="115" spans="1:16">
@@ -8437,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="P115" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="116" spans="1:16">
@@ -8487,7 +8490,7 @@
         <v>0</v>
       </c>
       <c r="P116" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="117" spans="1:16">
@@ -8537,7 +8540,7 @@
         <v>0</v>
       </c>
       <c r="P117" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="118" spans="1:16">
@@ -8587,7 +8590,7 @@
         <v>0</v>
       </c>
       <c r="P118" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="119" spans="1:16">
@@ -8637,7 +8640,7 @@
         <v>0</v>
       </c>
       <c r="P119" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="120" spans="1:16">
@@ -8687,7 +8690,7 @@
         <v>0</v>
       </c>
       <c r="P120" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="121" spans="1:16">
@@ -8737,7 +8740,7 @@
         <v>0</v>
       </c>
       <c r="P121" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="122" spans="1:16">
@@ -8787,7 +8790,7 @@
         <v>0</v>
       </c>
       <c r="P122" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="123" spans="1:16">
@@ -8837,7 +8840,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="124" spans="1:16">
@@ -8887,7 +8890,7 @@
         <v>0</v>
       </c>
       <c r="P124" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="125" spans="1:16">
@@ -8937,7 +8940,7 @@
         <v>0</v>
       </c>
       <c r="P125" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="126" spans="1:16">
@@ -8987,7 +8990,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="127" spans="1:16">
@@ -9037,7 +9040,7 @@
         <v>0</v>
       </c>
       <c r="P127" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="128" spans="1:16">
@@ -9087,7 +9090,7 @@
         <v>0</v>
       </c>
       <c r="P128" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="129" spans="1:16">
@@ -9137,7 +9140,7 @@
         <v>0</v>
       </c>
       <c r="P129" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="130" spans="1:16">
@@ -9187,7 +9190,7 @@
         <v>0</v>
       </c>
       <c r="P130" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="131" spans="1:16">
@@ -9237,7 +9240,7 @@
         <v>0</v>
       </c>
       <c r="P131" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="132" spans="1:16">
@@ -9287,7 +9290,7 @@
         <v>0</v>
       </c>
       <c r="P132" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="133" spans="1:16">
@@ -9337,7 +9340,7 @@
         <v>0</v>
       </c>
       <c r="P133" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="134" spans="1:16">
@@ -9387,7 +9390,7 @@
         <v>0</v>
       </c>
       <c r="P134" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="135" spans="1:16">
@@ -9437,7 +9440,7 @@
         <v>0</v>
       </c>
       <c r="P135" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="136" spans="1:16">
@@ -9487,7 +9490,7 @@
         <v>0</v>
       </c>
       <c r="P136" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="137" spans="1:16">
@@ -9537,7 +9540,7 @@
         <v>0</v>
       </c>
       <c r="P137" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="138" spans="1:16">
@@ -9587,7 +9590,7 @@
         <v>0</v>
       </c>
       <c r="P138" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="139" spans="1:16">
@@ -9637,7 +9640,7 @@
         <v>0</v>
       </c>
       <c r="P139" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="140" spans="1:16">
@@ -9687,7 +9690,7 @@
         <v>0</v>
       </c>
       <c r="P140" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="141" spans="1:16">
@@ -9737,7 +9740,7 @@
         <v>0</v>
       </c>
       <c r="P141" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="142" spans="1:16">
@@ -9787,7 +9790,7 @@
         <v>0</v>
       </c>
       <c r="P142" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="143" spans="1:16">
@@ -9837,7 +9840,7 @@
         <v>0</v>
       </c>
       <c r="P143" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="144" spans="1:16">
@@ -9887,7 +9890,7 @@
         <v>0</v>
       </c>
       <c r="P144" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="145" spans="1:16">
@@ -9937,7 +9940,7 @@
         <v>0</v>
       </c>
       <c r="P145" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="146" spans="1:16">
@@ -9987,7 +9990,7 @@
         <v>0</v>
       </c>
       <c r="P146" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="147" spans="1:16">
@@ -10037,7 +10040,7 @@
         <v>0</v>
       </c>
       <c r="P147" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="148" spans="1:16">
@@ -10087,7 +10090,7 @@
         <v>0</v>
       </c>
       <c r="P148" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="149" spans="1:16">
@@ -10137,7 +10140,7 @@
         <v>0</v>
       </c>
       <c r="P149" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="150" spans="1:16">
@@ -10187,7 +10190,7 @@
         <v>0</v>
       </c>
       <c r="P150" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="151" spans="1:16">
@@ -10237,7 +10240,7 @@
         <v>0</v>
       </c>
       <c r="P151" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="152" spans="1:16">
@@ -10287,7 +10290,7 @@
         <v>0</v>
       </c>
       <c r="P152" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="153" spans="1:16">
@@ -10337,7 +10340,7 @@
         <v>0</v>
       </c>
       <c r="P153" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="154" spans="1:16">
@@ -10387,7 +10390,7 @@
         <v>0</v>
       </c>
       <c r="P154" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="155" spans="1:16">
@@ -10437,7 +10440,7 @@
         <v>0</v>
       </c>
       <c r="P155" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="156" spans="1:16">
@@ -10487,7 +10490,7 @@
         <v>0</v>
       </c>
       <c r="P156" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="157" spans="1:16">
@@ -10537,7 +10540,7 @@
         <v>0</v>
       </c>
       <c r="P157" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="158" spans="1:16">
@@ -10587,7 +10590,7 @@
         <v>0</v>
       </c>
       <c r="P158" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="159" spans="1:16">
@@ -10637,7 +10640,7 @@
         <v>0</v>
       </c>
       <c r="P159" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="160" spans="1:16">
@@ -10687,7 +10690,7 @@
         <v>0</v>
       </c>
       <c r="P160" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="161" spans="1:16">
@@ -10716,7 +10719,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="P161" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="162" spans="1:16">
@@ -10745,7 +10748,7 @@
         <v>8.83</v>
       </c>
       <c r="P162" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="163" spans="1:16">
@@ -10774,7 +10777,7 @@
         <v>9.27</v>
       </c>
       <c r="P163" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="164" spans="1:16">
@@ -10824,7 +10827,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="165" spans="1:16">
@@ -10874,7 +10877,7 @@
         <v>0</v>
       </c>
       <c r="P165" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="166" spans="1:16">
@@ -10924,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="P166" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="167" spans="1:16">
@@ -10974,7 +10977,7 @@
         <v>1</v>
       </c>
       <c r="P167" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="168" spans="1:16">
@@ -11024,7 +11027,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="169" spans="1:16">
@@ -11074,7 +11077,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="170" spans="1:16">
@@ -11124,7 +11127,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="171" spans="1:16">
@@ -11174,7 +11177,7 @@
         <v>0</v>
       </c>
       <c r="P171" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="172" spans="1:16">
@@ -11224,7 +11227,7 @@
         <v>0</v>
       </c>
       <c r="P172" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="173" spans="1:16">
@@ -11274,7 +11277,7 @@
         <v>0</v>
       </c>
       <c r="P173" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="174" spans="1:16">
@@ -11324,7 +11327,7 @@
         <v>0</v>
       </c>
       <c r="P174" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="175" spans="1:16">
@@ -11374,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="P175" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="176" spans="1:16">
@@ -11424,7 +11427,7 @@
         <v>0</v>
       </c>
       <c r="P176" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="177" spans="1:16">
@@ -11474,7 +11477,7 @@
         <v>0</v>
       </c>
       <c r="P177" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="178" spans="1:16">
@@ -11524,7 +11527,7 @@
         <v>0</v>
       </c>
       <c r="P178" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="179" spans="1:16">
@@ -11574,7 +11577,7 @@
         <v>0</v>
       </c>
       <c r="P179" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="180" spans="1:16">
@@ -11624,7 +11627,7 @@
         <v>0</v>
       </c>
       <c r="P180" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="181" spans="1:16">
@@ -11674,7 +11677,7 @@
         <v>0</v>
       </c>
       <c r="P181" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="182" spans="1:16">
@@ -11724,7 +11727,7 @@
         <v>0</v>
       </c>
       <c r="P182" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="183" spans="1:16">
@@ -11774,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="P183" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="184" spans="1:16">
@@ -11824,7 +11827,7 @@
         <v>0</v>
       </c>
       <c r="P184" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="185" spans="1:16">
@@ -11874,7 +11877,7 @@
         <v>0</v>
       </c>
       <c r="P185" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="186" spans="1:16">
@@ -11924,7 +11927,7 @@
         <v>0</v>
       </c>
       <c r="P186" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="187" spans="1:16">
@@ -11974,7 +11977,7 @@
         <v>0</v>
       </c>
       <c r="P187" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="188" spans="1:16">
@@ -12024,7 +12027,7 @@
         <v>0</v>
       </c>
       <c r="P188" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="189" spans="1:16">
@@ -12074,7 +12077,7 @@
         <v>0</v>
       </c>
       <c r="P189" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="190" spans="1:16">
@@ -12124,7 +12127,7 @@
         <v>0</v>
       </c>
       <c r="P190" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="191" spans="1:16">
@@ -12174,7 +12177,7 @@
         <v>0</v>
       </c>
       <c r="P191" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="192" spans="1:16">
@@ -12224,7 +12227,7 @@
         <v>0</v>
       </c>
       <c r="P192" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="193" spans="1:16">
@@ -12274,7 +12277,7 @@
         <v>0</v>
       </c>
       <c r="P193" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="194" spans="1:16">
@@ -12474,7 +12477,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="198" spans="1:16">
@@ -12524,7 +12527,7 @@
         <v>0</v>
       </c>
       <c r="P198" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="199" spans="1:16">
@@ -12574,7 +12577,7 @@
         <v>0</v>
       </c>
       <c r="P199" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="200" spans="1:16">
@@ -12624,7 +12627,7 @@
         <v>0</v>
       </c>
       <c r="P200" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="201" spans="1:16">
@@ -12674,7 +12677,7 @@
         <v>0</v>
       </c>
       <c r="P201" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="202" spans="1:16">
@@ -12724,7 +12727,7 @@
         <v>0</v>
       </c>
       <c r="P202" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="203" spans="1:16">
@@ -12774,7 +12777,7 @@
         <v>0</v>
       </c>
       <c r="P203" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="204" spans="1:16">
@@ -12824,7 +12827,7 @@
         <v>0</v>
       </c>
       <c r="P204" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="205" spans="1:16">
@@ -12874,7 +12877,7 @@
         <v>0</v>
       </c>
       <c r="P205" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="206" spans="1:16">
@@ -12924,7 +12927,7 @@
         <v>0</v>
       </c>
       <c r="P206" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="207" spans="1:16">
@@ -12974,7 +12977,7 @@
         <v>0</v>
       </c>
       <c r="P207" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="208" spans="1:16">
@@ -14124,7 +14127,7 @@
         <v>0</v>
       </c>
       <c r="P230" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="231" spans="1:16">
@@ -14174,7 +14177,7 @@
         <v>0</v>
       </c>
       <c r="P231" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="232" spans="1:16">
@@ -14224,7 +14227,7 @@
         <v>0</v>
       </c>
       <c r="P232" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="233" spans="1:16">
@@ -14274,7 +14277,7 @@
         <v>0</v>
       </c>
       <c r="P233" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="234" spans="1:16">
@@ -14324,7 +14327,7 @@
         <v>1</v>
       </c>
       <c r="P234" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="235" spans="1:16">
@@ -14374,7 +14377,7 @@
         <v>1</v>
       </c>
       <c r="P235" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="236" spans="1:16">
@@ -14424,7 +14427,7 @@
         <v>1</v>
       </c>
       <c r="P236" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="237" spans="1:16">
@@ -14474,7 +14477,7 @@
         <v>1</v>
       </c>
       <c r="P237" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="238" spans="1:16">
@@ -14524,7 +14527,7 @@
         <v>1</v>
       </c>
       <c r="P238" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="239" spans="1:16">
@@ -14574,7 +14577,7 @@
         <v>1</v>
       </c>
       <c r="P239" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="240" spans="1:16">
@@ -14624,7 +14627,7 @@
         <v>0</v>
       </c>
       <c r="P240" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="241" spans="1:16">
@@ -14674,7 +14677,7 @@
         <v>0</v>
       </c>
       <c r="P241" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="242" spans="1:16">
@@ -14724,7 +14727,7 @@
         <v>0</v>
       </c>
       <c r="P242" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="243" spans="1:16">
@@ -14774,7 +14777,7 @@
         <v>0</v>
       </c>
       <c r="P243" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="244" spans="1:16">
@@ -14824,7 +14827,7 @@
         <v>0</v>
       </c>
       <c r="P244" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="245" spans="1:16">
@@ -14853,7 +14856,7 @@
         <v>10.56</v>
       </c>
       <c r="P245" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="246" spans="1:16">
@@ -14882,7 +14885,7 @@
         <v>10.44</v>
       </c>
       <c r="P246" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="247" spans="1:16">
@@ -14911,7 +14914,7 @@
         <v>10.38</v>
       </c>
       <c r="P247" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="248" spans="1:16">
@@ -14940,7 +14943,7 @@
         <v>10.74</v>
       </c>
       <c r="P248" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="249" spans="1:16">
@@ -14990,7 +14993,7 @@
         <v>0</v>
       </c>
       <c r="P249" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="250" spans="1:16">
@@ -15040,7 +15043,7 @@
         <v>0</v>
       </c>
       <c r="P250" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="251" spans="1:16">
@@ -15090,7 +15093,7 @@
         <v>0</v>
       </c>
       <c r="P251" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="252" spans="1:16">
@@ -15140,7 +15143,7 @@
         <v>0</v>
       </c>
       <c r="P252" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="253" spans="1:16">
@@ -15190,7 +15193,7 @@
         <v>0</v>
       </c>
       <c r="P253" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="254" spans="1:16">
@@ -15240,7 +15243,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="255" spans="1:16">
@@ -15290,7 +15293,7 @@
         <v>0</v>
       </c>
       <c r="P255" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="256" spans="1:16">
@@ -15340,7 +15343,7 @@
         <v>0</v>
       </c>
       <c r="P256" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="257" spans="1:16">
@@ -15390,7 +15393,7 @@
         <v>0</v>
       </c>
       <c r="P257" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="258" spans="1:16">
@@ -15440,7 +15443,7 @@
         <v>0</v>
       </c>
       <c r="P258" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="259" spans="1:16">
@@ -15490,7 +15493,7 @@
         <v>0</v>
       </c>
       <c r="P259" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="260" spans="1:16">
@@ -15540,7 +15543,7 @@
         <v>0</v>
       </c>
       <c r="P260" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="261" spans="1:16">
@@ -15590,7 +15593,7 @@
         <v>0</v>
       </c>
       <c r="P261" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="262" spans="1:16">
@@ -15640,7 +15643,7 @@
         <v>0</v>
       </c>
       <c r="P262" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="263" spans="1:16">
@@ -15690,7 +15693,7 @@
         <v>0</v>
       </c>
       <c r="P263" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="264" spans="1:16">
@@ -15740,7 +15743,7 @@
         <v>0</v>
       </c>
       <c r="P264" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="265" spans="1:16">
@@ -15790,7 +15793,7 @@
         <v>1</v>
       </c>
       <c r="P265" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="266" spans="1:16">
@@ -15840,7 +15843,7 @@
         <v>1</v>
       </c>
       <c r="P266" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="267" spans="1:16">
@@ -15890,7 +15893,7 @@
         <v>1</v>
       </c>
       <c r="P267" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="268" spans="1:16">
@@ -15940,7 +15943,7 @@
         <v>0</v>
       </c>
       <c r="P268" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="269" spans="1:16">
@@ -15990,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="P269" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="270" spans="1:16">
@@ -16019,7 +16022,7 @@
         <v>11.5</v>
       </c>
       <c r="P270" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="271" spans="1:16">
@@ -16048,7 +16051,7 @@
         <v>11.36</v>
       </c>
       <c r="P271" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="272" spans="1:16">
@@ -16077,7 +16080,7 @@
         <v>11.22</v>
       </c>
       <c r="P272" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="273" spans="1:16">
@@ -16106,7 +16109,7 @@
         <v>11.08</v>
       </c>
       <c r="P273" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="274" spans="1:16">
@@ -16156,7 +16159,7 @@
         <v>0</v>
       </c>
       <c r="P274" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="275" spans="1:16">
@@ -16206,7 +16209,7 @@
         <v>0</v>
       </c>
       <c r="P275" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="276" spans="1:16">
@@ -16256,7 +16259,7 @@
         <v>0</v>
       </c>
       <c r="P276" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="277" spans="1:16">
@@ -16456,7 +16459,7 @@
         <v>0</v>
       </c>
       <c r="P280" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="281" spans="1:16">
@@ -16506,7 +16509,7 @@
         <v>0</v>
       </c>
       <c r="P281" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="282" spans="1:16">
@@ -16556,7 +16559,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="283" spans="1:16">
@@ -16706,7 +16709,7 @@
         <v>0</v>
       </c>
       <c r="P285" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="286" spans="1:16">
@@ -16756,7 +16759,7 @@
         <v>0</v>
       </c>
       <c r="P286" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="287" spans="1:16">
@@ -16806,7 +16809,7 @@
         <v>1</v>
       </c>
       <c r="P287" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="288" spans="1:16">
@@ -16856,7 +16859,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="289" spans="1:16">
@@ -16906,7 +16909,7 @@
         <v>1</v>
       </c>
       <c r="P289" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="290" spans="1:16">
@@ -16956,7 +16959,7 @@
         <v>1</v>
       </c>
       <c r="P290" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="291" spans="1:16">
@@ -17006,7 +17009,7 @@
         <v>1</v>
       </c>
       <c r="P291" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="292" spans="1:16">
@@ -17056,7 +17059,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="293" spans="1:16">
@@ -17106,7 +17109,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="294" spans="1:16">
@@ -17156,7 +17159,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="295" spans="1:16">
@@ -17206,7 +17209,7 @@
         <v>1</v>
       </c>
       <c r="P295" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="296" spans="1:16">
@@ -17256,7 +17259,7 @@
         <v>1</v>
       </c>
       <c r="P296" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="297" spans="1:16">
@@ -17306,7 +17309,7 @@
         <v>1</v>
       </c>
       <c r="P297" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="298" spans="1:16">
@@ -17356,7 +17359,7 @@
         <v>1</v>
       </c>
       <c r="P298" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="299" spans="1:16">
@@ -17406,7 +17409,7 @@
         <v>1</v>
       </c>
       <c r="P299" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="300" spans="1:16">
@@ -17456,7 +17459,7 @@
         <v>1</v>
       </c>
       <c r="P300" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="301" spans="1:16">
@@ -17506,7 +17509,7 @@
         <v>1</v>
       </c>
       <c r="P301" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="302" spans="1:16">
@@ -17556,7 +17559,7 @@
         <v>1</v>
       </c>
       <c r="P302" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="303" spans="1:16">
@@ -17606,7 +17609,7 @@
         <v>1</v>
       </c>
       <c r="P303" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="304" spans="1:16">
@@ -17656,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="P304" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="305" spans="1:16">
@@ -17706,7 +17709,7 @@
         <v>1</v>
       </c>
       <c r="P305" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="306" spans="1:16">
@@ -17756,7 +17759,7 @@
         <v>1</v>
       </c>
       <c r="P306" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="307" spans="1:16">
@@ -17806,7 +17809,7 @@
         <v>1</v>
       </c>
       <c r="P307" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="308" spans="1:16">
@@ -17856,7 +17859,7 @@
         <v>1</v>
       </c>
       <c r="P308" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="309" spans="1:16">
@@ -17906,7 +17909,7 @@
         <v>1</v>
       </c>
       <c r="P309" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="310" spans="1:16">
@@ -17956,7 +17959,7 @@
         <v>1</v>
       </c>
       <c r="P310" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="311" spans="1:16">
@@ -18006,7 +18009,7 @@
         <v>1</v>
       </c>
       <c r="P311" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="312" spans="1:16">
@@ -18056,7 +18059,7 @@
         <v>1</v>
       </c>
       <c r="P312" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="313" spans="1:16">
@@ -18106,7 +18109,7 @@
         <v>0</v>
       </c>
       <c r="P313" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="314" spans="1:16">
@@ -18156,7 +18159,7 @@
         <v>0</v>
       </c>
       <c r="P314" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="315" spans="1:16">
@@ -18206,7 +18209,7 @@
         <v>0</v>
       </c>
       <c r="P315" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="316" spans="1:16">
@@ -18256,7 +18259,7 @@
         <v>0</v>
       </c>
       <c r="P316" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="317" spans="1:16">
@@ -18306,7 +18309,7 @@
         <v>0</v>
       </c>
       <c r="P317" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="318" spans="1:16">
@@ -18356,7 +18359,7 @@
         <v>0</v>
       </c>
       <c r="P318" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="319" spans="1:16">
@@ -18406,7 +18409,7 @@
         <v>0</v>
       </c>
       <c r="P319" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="320" spans="1:16">
@@ -18456,7 +18459,7 @@
         <v>0</v>
       </c>
       <c r="P320" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="321" spans="1:16">
@@ -18506,7 +18509,7 @@
         <v>0</v>
       </c>
       <c r="P321" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="322" spans="1:16">
@@ -18556,7 +18559,7 @@
         <v>0</v>
       </c>
       <c r="P322" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="323" spans="1:16">
@@ -18756,7 +18759,7 @@
         <v>1</v>
       </c>
       <c r="P326" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="327" spans="1:16">
@@ -18806,7 +18809,7 @@
         <v>1</v>
       </c>
       <c r="P327" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="328" spans="1:16">
@@ -18856,7 +18859,7 @@
         <v>1</v>
       </c>
       <c r="P328" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="329" spans="1:16">
@@ -19106,7 +19109,7 @@
         <v>1</v>
       </c>
       <c r="P333" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="334" spans="1:16">
@@ -19156,7 +19159,7 @@
         <v>1</v>
       </c>
       <c r="P334" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="335" spans="1:16">
@@ -19206,7 +19209,7 @@
         <v>1</v>
       </c>
       <c r="P335" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="336" spans="1:16">
@@ -19256,7 +19259,7 @@
         <v>1</v>
       </c>
       <c r="P336" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="337" spans="1:16">
@@ -19306,7 +19309,7 @@
         <v>1</v>
       </c>
       <c r="P337" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="338" spans="1:16">
@@ -19356,7 +19359,7 @@
         <v>1</v>
       </c>
       <c r="P338" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="339" spans="1:16">
@@ -19406,7 +19409,7 @@
         <v>1</v>
       </c>
       <c r="P339" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="340" spans="1:16">
@@ -19456,7 +19459,7 @@
         <v>1</v>
       </c>
       <c r="P340" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="341" spans="1:16">
@@ -19506,7 +19509,7 @@
         <v>1</v>
       </c>
       <c r="P341" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="342" spans="1:16">
@@ -19556,7 +19559,7 @@
         <v>1</v>
       </c>
       <c r="P342" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="343" spans="1:16">
@@ -19606,7 +19609,7 @@
         <v>1</v>
       </c>
       <c r="P343" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="344" spans="1:16">
@@ -19656,7 +19659,7 @@
         <v>1</v>
       </c>
       <c r="P344" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="345" spans="1:16">
@@ -19706,7 +19709,7 @@
         <v>1</v>
       </c>
       <c r="P345" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="346" spans="1:16">
@@ -19756,7 +19759,7 @@
         <v>1</v>
       </c>
       <c r="P346" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="347" spans="1:16">
@@ -19806,7 +19809,7 @@
         <v>1</v>
       </c>
       <c r="P347" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="348" spans="1:16">
@@ -19856,7 +19859,7 @@
         <v>1</v>
       </c>
       <c r="P348" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="349" spans="1:16">
@@ -19906,7 +19909,7 @@
         <v>1</v>
       </c>
       <c r="P349" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="350" spans="1:16">
@@ -19956,7 +19959,7 @@
         <v>1</v>
       </c>
       <c r="P350" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="351" spans="1:16">
@@ -20006,7 +20009,7 @@
         <v>1</v>
       </c>
       <c r="P351" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="352" spans="1:16">
@@ -20056,7 +20059,7 @@
         <v>1</v>
       </c>
       <c r="P352" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="353" spans="1:16">
@@ -20106,7 +20109,7 @@
         <v>1</v>
       </c>
       <c r="P353" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="354" spans="1:16">
@@ -20156,7 +20159,7 @@
         <v>1</v>
       </c>
       <c r="P354" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="355" spans="1:16">
@@ -20206,7 +20209,7 @@
         <v>1</v>
       </c>
       <c r="P355" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="356" spans="1:16">
@@ -20256,7 +20259,7 @@
         <v>1</v>
       </c>
       <c r="P356" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="357" spans="1:16">
@@ -20306,7 +20309,7 @@
         <v>1</v>
       </c>
       <c r="P357" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="358" spans="1:16">
@@ -20356,7 +20359,7 @@
         <v>1</v>
       </c>
       <c r="P358" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="359" spans="1:16">
@@ -20406,7 +20409,7 @@
         <v>1</v>
       </c>
       <c r="P359" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="360" spans="1:16">
@@ -20556,7 +20559,7 @@
         <v>0</v>
       </c>
       <c r="P362" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="363" spans="1:16">
@@ -20606,7 +20609,7 @@
         <v>0</v>
       </c>
       <c r="P363" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="364" spans="1:16">
@@ -20656,7 +20659,7 @@
         <v>0</v>
       </c>
       <c r="P364" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="365" spans="1:16">
@@ -20706,7 +20709,7 @@
         <v>0</v>
       </c>
       <c r="P365" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="366" spans="1:16">
@@ -20756,7 +20759,7 @@
         <v>0</v>
       </c>
       <c r="P366" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="367" spans="1:16">
@@ -20806,7 +20809,7 @@
         <v>0</v>
       </c>
       <c r="P367" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="368" spans="1:16">
@@ -20856,7 +20859,7 @@
         <v>0</v>
       </c>
       <c r="P368" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="369" spans="1:16">
@@ -20906,7 +20909,7 @@
         <v>0</v>
       </c>
       <c r="P369" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="370" spans="1:16">
@@ -20956,7 +20959,7 @@
         <v>0</v>
       </c>
       <c r="P370" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="371" spans="1:16">
@@ -21006,7 +21009,7 @@
         <v>0</v>
       </c>
       <c r="P371" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="372" spans="1:16">
@@ -21456,7 +21459,7 @@
         <v>0</v>
       </c>
       <c r="P380" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="381" spans="1:16">
@@ -21506,7 +21509,7 @@
         <v>0</v>
       </c>
       <c r="P381" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="382" spans="1:16">
@@ -21556,7 +21559,7 @@
         <v>0</v>
       </c>
       <c r="P382" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="383" spans="1:16">
@@ -21606,7 +21609,7 @@
         <v>0</v>
       </c>
       <c r="P383" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="384" spans="1:16">
@@ -21656,7 +21659,7 @@
         <v>0</v>
       </c>
       <c r="P384" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="385" spans="1:16">
@@ -21706,7 +21709,7 @@
         <v>0</v>
       </c>
       <c r="P385" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="386" spans="1:16">
@@ -21756,7 +21759,7 @@
         <v>0</v>
       </c>
       <c r="P386" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="387" spans="1:16">
@@ -21806,7 +21809,7 @@
         <v>0</v>
       </c>
       <c r="P387" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="388" spans="1:16">
@@ -21856,7 +21859,7 @@
         <v>0</v>
       </c>
       <c r="P388" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="389" spans="1:16">
@@ -21906,7 +21909,7 @@
         <v>1</v>
       </c>
       <c r="P389" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="390" spans="1:16">
@@ -21956,7 +21959,7 @@
         <v>0</v>
       </c>
       <c r="P390" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="391" spans="1:16">
@@ -22006,7 +22009,7 @@
         <v>1</v>
       </c>
       <c r="P391" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="392" spans="1:16">
@@ -22056,7 +22059,7 @@
         <v>0</v>
       </c>
       <c r="P392" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="393" spans="1:16">
@@ -22106,7 +22109,7 @@
         <v>1</v>
       </c>
       <c r="P393" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="394" spans="1:16">
@@ -22156,7 +22159,7 @@
         <v>0</v>
       </c>
       <c r="P394" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="395" spans="1:16">
@@ -22206,7 +22209,7 @@
         <v>1</v>
       </c>
       <c r="P395" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="396" spans="1:16">
@@ -22256,7 +22259,7 @@
         <v>1</v>
       </c>
       <c r="P396" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="397" spans="1:16">
@@ -22306,7 +22309,7 @@
         <v>1</v>
       </c>
       <c r="P397" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="398" spans="1:16">
@@ -22356,7 +22359,7 @@
         <v>1</v>
       </c>
       <c r="P398" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="399" spans="1:16">
@@ -22406,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="P399" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="400" spans="1:16">
@@ -22456,7 +22459,7 @@
         <v>1</v>
       </c>
       <c r="P400" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="401" spans="1:16">
@@ -22506,7 +22509,7 @@
         <v>1</v>
       </c>
       <c r="P401" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="402" spans="1:16">
@@ -22556,7 +22559,7 @@
         <v>1</v>
       </c>
       <c r="P402" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="403" spans="1:16">
@@ -22606,7 +22609,7 @@
         <v>1</v>
       </c>
       <c r="P403" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="404" spans="1:16">
@@ -22656,7 +22659,7 @@
         <v>1</v>
       </c>
       <c r="P404" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="405" spans="1:16">
@@ -22706,7 +22709,7 @@
         <v>1</v>
       </c>
       <c r="P405" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="406" spans="1:16">
@@ -22756,7 +22759,7 @@
         <v>1</v>
       </c>
       <c r="P406" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="407" spans="1:16">
@@ -22806,7 +22809,7 @@
         <v>1</v>
       </c>
       <c r="P407" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="408" spans="1:16">
@@ -22856,7 +22859,7 @@
         <v>1</v>
       </c>
       <c r="P408" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="409" spans="1:16">
@@ -22956,7 +22959,7 @@
         <v>1</v>
       </c>
       <c r="P410" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="411" spans="1:16">
@@ -23006,7 +23009,7 @@
         <v>1</v>
       </c>
       <c r="P411" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="412" spans="1:16">
@@ -23056,7 +23059,7 @@
         <v>1</v>
       </c>
       <c r="P412" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="413" spans="1:16">
@@ -23106,7 +23109,7 @@
         <v>1</v>
       </c>
       <c r="P413" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="414" spans="1:16">
@@ -23156,7 +23159,7 @@
         <v>1</v>
       </c>
       <c r="P414" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="415" spans="1:16">
@@ -23206,7 +23209,7 @@
         <v>1</v>
       </c>
       <c r="P415" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="416" spans="1:16">
@@ -23256,7 +23259,7 @@
         <v>1</v>
       </c>
       <c r="P416" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="417" spans="1:16">
@@ -23306,7 +23309,7 @@
         <v>1</v>
       </c>
       <c r="P417" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="418" spans="1:16">
@@ -23356,7 +23359,7 @@
         <v>1</v>
       </c>
       <c r="P418" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="419" spans="1:16">
@@ -23406,7 +23409,7 @@
         <v>1</v>
       </c>
       <c r="P419" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="420" spans="1:16">
@@ -23456,7 +23459,7 @@
         <v>1</v>
       </c>
       <c r="P420" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
     </row>
     <row r="421" spans="1:16">
@@ -23506,7 +23509,7 @@
         <v>1</v>
       </c>
       <c r="P421" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="422" spans="1:16">
@@ -23556,7 +23559,7 @@
         <v>1</v>
       </c>
       <c r="P422" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="423" spans="1:16">
@@ -23606,7 +23609,7 @@
         <v>1</v>
       </c>
       <c r="P423" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="424" spans="1:16">
@@ -23656,7 +23659,7 @@
         <v>1</v>
       </c>
       <c r="P424" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="425" spans="1:16">
@@ -23706,7 +23709,7 @@
         <v>1</v>
       </c>
       <c r="P425" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="426" spans="1:16">
@@ -23756,7 +23759,7 @@
         <v>1</v>
       </c>
       <c r="P426" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="427" spans="1:16">
@@ -23806,7 +23809,7 @@
         <v>1</v>
       </c>
       <c r="P427" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="428" spans="1:16">
@@ -23835,7 +23838,7 @@
         <v>5.49</v>
       </c>
       <c r="P428" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
     </row>
     <row r="429" spans="1:16">
@@ -23885,7 +23888,7 @@
         <v>1</v>
       </c>
       <c r="P429" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="430" spans="1:16">
@@ -23935,7 +23938,7 @@
         <v>1</v>
       </c>
       <c r="P430" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="431" spans="1:16">
@@ -23985,7 +23988,7 @@
         <v>1</v>
       </c>
       <c r="P431" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="432" spans="1:16">
@@ -24035,7 +24038,7 @@
         <v>0</v>
       </c>
       <c r="P432" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="433" spans="1:16">
@@ -24085,7 +24088,7 @@
         <v>1</v>
       </c>
       <c r="P433" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="434" spans="1:16">
@@ -24135,7 +24138,7 @@
         <v>1</v>
       </c>
       <c r="P434" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="435" spans="1:16">
@@ -24185,7 +24188,7 @@
         <v>1</v>
       </c>
       <c r="P435" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="436" spans="1:16">
@@ -24235,7 +24238,7 @@
         <v>0</v>
       </c>
       <c r="P436" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
     </row>
     <row r="437" spans="1:16">
@@ -24285,7 +24288,7 @@
         <v>1</v>
       </c>
       <c r="P437" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="438" spans="1:16">
@@ -24335,7 +24338,7 @@
         <v>1</v>
       </c>
       <c r="P438" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="439" spans="1:16">
@@ -24385,7 +24388,7 @@
         <v>1</v>
       </c>
       <c r="P439" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="440" spans="1:16">
@@ -24435,7 +24438,7 @@
         <v>0</v>
       </c>
       <c r="P440" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="441" spans="1:16">
@@ -24485,7 +24488,7 @@
         <v>1</v>
       </c>
       <c r="P441" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="442" spans="1:16">
@@ -24535,7 +24538,7 @@
         <v>1</v>
       </c>
       <c r="P442" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="443" spans="1:16">
@@ -24585,7 +24588,7 @@
         <v>0</v>
       </c>
       <c r="P443" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
     </row>
     <row r="444" spans="1:16">
@@ -24635,7 +24638,7 @@
         <v>1</v>
       </c>
       <c r="P444" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="445" spans="1:16">
@@ -24685,7 +24688,7 @@
         <v>1</v>
       </c>
       <c r="P445" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="446" spans="1:16">
@@ -24735,7 +24738,7 @@
         <v>0</v>
       </c>
       <c r="P446" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="447" spans="1:16">
@@ -24785,7 +24788,7 @@
         <v>1</v>
       </c>
       <c r="P447" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
     </row>
     <row r="448" spans="1:16">
@@ -24835,7 +24838,7 @@
         <v>1</v>
       </c>
       <c r="P448" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="449" spans="1:16">
@@ -24885,7 +24888,7 @@
         <v>1</v>
       </c>
       <c r="P449" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
     </row>
     <row r="450" spans="1:16">
@@ -24935,7 +24938,7 @@
         <v>1</v>
       </c>
       <c r="P450" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="451" spans="1:16">
@@ -24985,7 +24988,7 @@
         <v>1</v>
       </c>
       <c r="P451" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="452" spans="1:16">
@@ -25035,7 +25038,7 @@
         <v>1</v>
       </c>
       <c r="P452" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="453" spans="1:16">
@@ -25085,7 +25088,7 @@
         <v>1</v>
       </c>
       <c r="P453" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="454" spans="1:16">
@@ -25135,7 +25138,7 @@
         <v>1</v>
       </c>
       <c r="P454" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="455" spans="1:16">
@@ -25185,7 +25188,7 @@
         <v>1</v>
       </c>
       <c r="P455" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="456" spans="1:16">
@@ -25235,7 +25238,7 @@
         <v>1</v>
       </c>
       <c r="P456" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
     </row>
     <row r="457" spans="1:16">
@@ -25285,7 +25288,7 @@
         <v>1</v>
       </c>
       <c r="P457" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="458" spans="1:16">
@@ -25335,7 +25338,7 @@
         <v>1</v>
       </c>
       <c r="P458" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="459" spans="1:16">
@@ -25385,7 +25388,7 @@
         <v>1</v>
       </c>
       <c r="P459" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
     </row>
     <row r="460" spans="1:16">
@@ -25435,7 +25438,7 @@
         <v>1</v>
       </c>
       <c r="P460" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="461" spans="1:16">
@@ -25485,7 +25488,7 @@
         <v>0</v>
       </c>
       <c r="P461" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="462" spans="1:16">
@@ -25535,7 +25538,7 @@
         <v>0</v>
       </c>
       <c r="P462" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="463" spans="1:16">
@@ -25585,7 +25588,7 @@
         <v>0</v>
       </c>
       <c r="P463" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="464" spans="1:16">
@@ -25635,7 +25638,7 @@
         <v>0</v>
       </c>
       <c r="P464" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="465" spans="1:16">
@@ -25935,7 +25938,7 @@
         <v>1</v>
       </c>
       <c r="P470" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="471" spans="1:16">
@@ -25985,7 +25988,7 @@
         <v>0</v>
       </c>
       <c r="P471" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="472" spans="1:16">
@@ -26035,7 +26038,7 @@
         <v>0</v>
       </c>
       <c r="P472" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="473" spans="1:16">
@@ -26085,7 +26088,7 @@
         <v>0</v>
       </c>
       <c r="P473" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="474" spans="1:16">
@@ -26135,7 +26138,7 @@
         <v>0</v>
       </c>
       <c r="P474" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
     </row>
     <row r="475" spans="1:16">
@@ -26185,7 +26188,7 @@
         <v>1</v>
       </c>
       <c r="P475" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="476" spans="1:16">
@@ -26235,7 +26238,7 @@
         <v>1</v>
       </c>
       <c r="P476" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="477" spans="1:16">
@@ -26285,7 +26288,7 @@
         <v>0</v>
       </c>
       <c r="P477" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="478" spans="1:16">
@@ -26335,7 +26338,7 @@
         <v>0</v>
       </c>
       <c r="P478" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="479" spans="1:16">
@@ -26385,7 +26388,7 @@
         <v>0</v>
       </c>
       <c r="P479" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="480" spans="1:16">
@@ -26635,7 +26638,7 @@
         <v>1</v>
       </c>
       <c r="P484" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="485" spans="1:16">
@@ -26685,7 +26688,7 @@
         <v>0</v>
       </c>
       <c r="P485" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="486" spans="1:16">
@@ -26735,7 +26738,7 @@
         <v>0</v>
       </c>
       <c r="P486" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="487" spans="1:16">
@@ -26785,7 +26788,7 @@
         <v>0</v>
       </c>
       <c r="P487" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
     </row>
     <row r="488" spans="1:16">
@@ -26835,7 +26838,7 @@
         <v>1</v>
       </c>
       <c r="P488" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="489" spans="1:16">
@@ -26885,7 +26888,7 @@
         <v>1</v>
       </c>
       <c r="P489" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="490" spans="1:16">
@@ -26935,7 +26938,7 @@
         <v>1</v>
       </c>
       <c r="P490" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="491" spans="1:16">
@@ -26985,7 +26988,7 @@
         <v>1</v>
       </c>
       <c r="P491" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="492" spans="1:16">
@@ -27035,7 +27038,7 @@
         <v>1</v>
       </c>
       <c r="P492" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="493" spans="1:16">
@@ -27085,7 +27088,7 @@
         <v>0</v>
       </c>
       <c r="P493" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="494" spans="1:16">
@@ -27135,7 +27138,7 @@
         <v>1</v>
       </c>
       <c r="P494" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="495" spans="1:16">
@@ -27185,7 +27188,7 @@
         <v>0</v>
       </c>
       <c r="P495" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="496" spans="1:16">
@@ -27385,7 +27388,7 @@
         <v>1</v>
       </c>
       <c r="P499" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="500" spans="1:16">
@@ -27435,7 +27438,7 @@
         <v>1</v>
       </c>
       <c r="P500" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="501" spans="1:16">
@@ -27485,7 +27488,7 @@
         <v>1</v>
       </c>
       <c r="P501" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="502" spans="1:16">
@@ -27535,7 +27538,7 @@
         <v>1</v>
       </c>
       <c r="P502" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="503" spans="1:16">
@@ -27585,7 +27588,7 @@
         <v>1</v>
       </c>
       <c r="P503" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="504" spans="1:16">
@@ -27635,7 +27638,7 @@
         <v>1</v>
       </c>
       <c r="P504" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="505" spans="1:16">
@@ -27685,7 +27688,7 @@
         <v>1</v>
       </c>
       <c r="P505" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="506" spans="1:16">
@@ -27735,7 +27738,7 @@
         <v>1</v>
       </c>
       <c r="P506" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="507" spans="1:16">
@@ -27785,7 +27788,7 @@
         <v>1</v>
       </c>
       <c r="P507" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="508" spans="1:16">
@@ -27835,7 +27838,7 @@
         <v>1</v>
       </c>
       <c r="P508" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="509" spans="1:16">
@@ -27885,7 +27888,7 @@
         <v>1</v>
       </c>
       <c r="P509" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="510" spans="1:16">
@@ -27935,7 +27938,7 @@
         <v>1</v>
       </c>
       <c r="P510" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="511" spans="1:16">
@@ -27985,7 +27988,7 @@
         <v>1</v>
       </c>
       <c r="P511" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="512" spans="1:16">
@@ -28035,7 +28038,7 @@
         <v>1</v>
       </c>
       <c r="P512" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="513" spans="1:16">
@@ -28085,7 +28088,7 @@
         <v>1</v>
       </c>
       <c r="P513" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="514" spans="1:16">
@@ -28135,7 +28138,7 @@
         <v>1</v>
       </c>
       <c r="P514" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="515" spans="1:16">
@@ -28185,7 +28188,7 @@
         <v>1</v>
       </c>
       <c r="P515" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="516" spans="1:16">
@@ -28235,7 +28238,7 @@
         <v>1</v>
       </c>
       <c r="P516" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="517" spans="1:16">
@@ -28285,7 +28288,7 @@
         <v>0</v>
       </c>
       <c r="P517" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="518" spans="1:16">
@@ -28314,7 +28317,7 @@
         <v>5.37</v>
       </c>
       <c r="P518" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="519" spans="1:16">
@@ -28343,7 +28346,7 @@
         <v>5.6</v>
       </c>
       <c r="P519" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="520" spans="1:16">
@@ -28393,7 +28396,7 @@
         <v>0</v>
       </c>
       <c r="P520" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="521" spans="1:16">
@@ -28443,7 +28446,7 @@
         <v>0</v>
       </c>
       <c r="P521" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="522" spans="1:16">
@@ -28472,7 +28475,7 @@
         <v>5.37</v>
       </c>
       <c r="P522" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="523" spans="1:16">
@@ -28501,7 +28504,7 @@
         <v>5.6</v>
       </c>
       <c r="P523" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="524" spans="1:16">
@@ -28530,7 +28533,7 @@
         <v>5.77</v>
       </c>
       <c r="P524" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="525" spans="1:16">
@@ -28580,7 +28583,7 @@
         <v>0</v>
       </c>
       <c r="P525" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="526" spans="1:16">
@@ -28630,7 +28633,7 @@
         <v>0</v>
       </c>
       <c r="P526" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="527" spans="1:16">
@@ -28680,7 +28683,7 @@
         <v>0</v>
       </c>
       <c r="P527" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="528" spans="1:16">
@@ -28730,7 +28733,7 @@
         <v>0</v>
       </c>
       <c r="P528" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="529" spans="1:16">
@@ -28780,7 +28783,7 @@
         <v>0</v>
       </c>
       <c r="P529" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="530" spans="1:16">
@@ -28830,7 +28833,7 @@
         <v>0</v>
       </c>
       <c r="P530" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="531" spans="1:16">
@@ -29030,7 +29033,7 @@
         <v>0</v>
       </c>
       <c r="P534" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="535" spans="1:16">
@@ -29080,7 +29083,7 @@
         <v>0</v>
       </c>
       <c r="P535" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="536" spans="1:16">
@@ -29130,7 +29133,7 @@
         <v>0</v>
       </c>
       <c r="P536" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="537" spans="1:16">
@@ -29180,7 +29183,7 @@
         <v>0</v>
       </c>
       <c r="P537" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="538" spans="1:16">
@@ -29230,7 +29233,7 @@
         <v>0</v>
       </c>
       <c r="P538" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="539" spans="1:16">
@@ -29280,7 +29283,7 @@
         <v>0</v>
       </c>
       <c r="P539" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="540" spans="1:16">
@@ -29330,7 +29333,7 @@
         <v>0</v>
       </c>
       <c r="P540" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="541" spans="1:16">
@@ -29380,7 +29383,7 @@
         <v>1</v>
       </c>
       <c r="P541" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="542" spans="1:16">
@@ -29430,7 +29433,7 @@
         <v>1</v>
       </c>
       <c r="P542" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="543" spans="1:16">
@@ -29480,7 +29483,7 @@
         <v>0</v>
       </c>
       <c r="P543" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="544" spans="1:16">
@@ -29530,7 +29533,7 @@
         <v>0</v>
       </c>
       <c r="P544" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="545" spans="1:16">
@@ -29580,7 +29583,7 @@
         <v>0</v>
       </c>
       <c r="P545" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="546" spans="1:16">
@@ -29630,7 +29633,7 @@
         <v>1</v>
       </c>
       <c r="P546" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="547" spans="1:16">
@@ -29680,7 +29683,7 @@
         <v>1</v>
       </c>
       <c r="P547" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="548" spans="1:16">
@@ -29730,7 +29733,7 @@
         <v>1</v>
       </c>
       <c r="P548" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="549" spans="1:16">
@@ -29780,7 +29783,7 @@
         <v>0</v>
       </c>
       <c r="P549" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="550" spans="1:16">
@@ -29830,7 +29833,7 @@
         <v>0</v>
       </c>
       <c r="P550" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="551" spans="1:16">
@@ -29880,7 +29883,7 @@
         <v>0</v>
       </c>
       <c r="P551" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="552" spans="1:16">
@@ -29909,7 +29912,7 @@
         <v>6.55</v>
       </c>
       <c r="P552" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="553" spans="1:16">
@@ -29938,7 +29941,7 @@
         <v>6.7</v>
       </c>
       <c r="P553" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="554" spans="1:16">
@@ -29988,7 +29991,7 @@
         <v>0</v>
       </c>
       <c r="P554" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="555" spans="1:16">
@@ -30038,7 +30041,7 @@
         <v>0</v>
       </c>
       <c r="P555" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="556" spans="1:16">
@@ -30088,7 +30091,7 @@
         <v>0</v>
       </c>
       <c r="P556" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="557" spans="1:16">
@@ -30138,7 +30141,7 @@
         <v>0</v>
       </c>
       <c r="P557" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="558" spans="1:16">
@@ -30188,7 +30191,7 @@
         <v>0</v>
       </c>
       <c r="P558" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="559" spans="1:16">
@@ -30288,7 +30291,7 @@
         <v>0</v>
       </c>
       <c r="P560" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="561" spans="1:16">
@@ -30338,7 +30341,7 @@
         <v>0</v>
       </c>
       <c r="P561" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="562" spans="1:16">
@@ -30388,7 +30391,7 @@
         <v>0</v>
       </c>
       <c r="P562" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="563" spans="1:16">
@@ -30538,7 +30541,7 @@
         <v>1</v>
       </c>
       <c r="P565" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="566" spans="1:16">
@@ -30588,7 +30591,7 @@
         <v>1</v>
       </c>
       <c r="P566" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="567" spans="1:16">
@@ -30638,7 +30641,7 @@
         <v>1</v>
       </c>
       <c r="P567" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="568" spans="1:16">
@@ -30688,7 +30691,7 @@
         <v>0</v>
       </c>
       <c r="P568" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="569" spans="1:16">
@@ -30738,7 +30741,7 @@
         <v>0</v>
       </c>
       <c r="P569" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="570" spans="1:16">
@@ -30788,7 +30791,7 @@
         <v>1</v>
       </c>
       <c r="P570" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="571" spans="1:16">
@@ -30838,7 +30841,7 @@
         <v>0</v>
       </c>
       <c r="P571" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="572" spans="1:16">
@@ -30888,7 +30891,7 @@
         <v>0</v>
       </c>
       <c r="P572" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="573" spans="1:16">
@@ -30938,7 +30941,7 @@
         <v>0</v>
       </c>
       <c r="P573" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="574" spans="1:16">
@@ -30988,7 +30991,7 @@
         <v>0</v>
       </c>
       <c r="P574" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="575" spans="1:16">
@@ -31088,7 +31091,7 @@
         <v>1</v>
       </c>
       <c r="P576" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="577" spans="1:16">
@@ -31138,7 +31141,7 @@
         <v>1</v>
       </c>
       <c r="P577" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="578" spans="1:16">
@@ -31188,7 +31191,7 @@
         <v>1</v>
       </c>
       <c r="P578" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="579" spans="1:16">
@@ -31238,7 +31241,7 @@
         <v>1</v>
       </c>
       <c r="P579" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="580" spans="1:16">
@@ -31288,7 +31291,7 @@
         <v>0</v>
       </c>
       <c r="P580" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="581" spans="1:16">
@@ -31338,7 +31341,7 @@
         <v>0</v>
       </c>
       <c r="P581" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="582" spans="1:16">
@@ -31388,7 +31391,7 @@
         <v>1</v>
       </c>
       <c r="P582" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="583" spans="1:16">
@@ -31438,7 +31441,7 @@
         <v>1</v>
       </c>
       <c r="P583" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="584" spans="1:16">
@@ -31488,7 +31491,7 @@
         <v>0</v>
       </c>
       <c r="P584" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="585" spans="1:16">
@@ -31538,7 +31541,7 @@
         <v>0</v>
       </c>
       <c r="P585" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="586" spans="1:16">
@@ -31588,7 +31591,7 @@
         <v>0</v>
       </c>
       <c r="P586" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="587" spans="1:16">
@@ -31638,7 +31641,7 @@
         <v>0</v>
       </c>
       <c r="P587" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="588" spans="1:16">
@@ -31688,7 +31691,7 @@
         <v>0</v>
       </c>
       <c r="P588" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="589" spans="1:16">
@@ -31738,7 +31741,7 @@
         <v>0</v>
       </c>
       <c r="P589" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="590" spans="1:16">
@@ -31788,7 +31791,7 @@
         <v>0</v>
       </c>
       <c r="P590" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="591" spans="1:16">
@@ -31838,7 +31841,7 @@
         <v>0</v>
       </c>
       <c r="P591" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="592" spans="1:16">
@@ -31888,7 +31891,7 @@
         <v>1</v>
       </c>
       <c r="P592" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="593" spans="1:16">
@@ -31938,7 +31941,7 @@
         <v>0</v>
       </c>
       <c r="P593" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="594" spans="1:16">
@@ -31988,7 +31991,7 @@
         <v>0</v>
       </c>
       <c r="P594" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="595" spans="1:16">
@@ -32038,7 +32041,7 @@
         <v>1</v>
       </c>
       <c r="P595" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="596" spans="1:16">
@@ -32088,7 +32091,7 @@
         <v>1</v>
       </c>
       <c r="P596" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="597" spans="1:16">
@@ -32138,7 +32141,7 @@
         <v>1</v>
       </c>
       <c r="P597" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="598" spans="1:16">
@@ -32188,7 +32191,7 @@
         <v>1</v>
       </c>
       <c r="P598" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="599" spans="1:16">
@@ -32238,7 +32241,7 @@
         <v>1</v>
       </c>
       <c r="P599" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="600" spans="1:16">
@@ -32288,7 +32291,7 @@
         <v>1</v>
       </c>
       <c r="P600" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="601" spans="1:16">
@@ -32338,7 +32341,7 @@
         <v>1</v>
       </c>
       <c r="P601" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="602" spans="1:16">
@@ -32388,7 +32391,7 @@
         <v>1</v>
       </c>
       <c r="P602" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="603" spans="1:16">
@@ -32438,7 +32441,7 @@
         <v>1</v>
       </c>
       <c r="P603" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="604" spans="1:16">
@@ -32488,7 +32491,7 @@
         <v>1</v>
       </c>
       <c r="P604" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="605" spans="1:16">
@@ -32538,7 +32541,7 @@
         <v>1</v>
       </c>
       <c r="P605" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="606" spans="1:16">
@@ -32588,7 +32591,7 @@
         <v>1</v>
       </c>
       <c r="P606" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="607" spans="1:16">
@@ -32638,7 +32641,7 @@
         <v>1</v>
       </c>
       <c r="P607" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="608" spans="1:16">
@@ -32688,7 +32691,7 @@
         <v>1</v>
       </c>
       <c r="P608" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="609" spans="1:16">
@@ -32738,7 +32741,7 @@
         <v>1</v>
       </c>
       <c r="P609" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="610" spans="1:16">
@@ -32788,7 +32791,7 @@
         <v>1</v>
       </c>
       <c r="P610" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="611" spans="1:16">
@@ -32838,7 +32841,7 @@
         <v>1</v>
       </c>
       <c r="P611" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="612" spans="1:16">
@@ -32888,7 +32891,7 @@
         <v>1</v>
       </c>
       <c r="P612" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="613" spans="1:16">
@@ -32938,7 +32941,7 @@
         <v>1</v>
       </c>
       <c r="P613" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="614" spans="1:16">
@@ -33738,7 +33741,7 @@
         <v>1</v>
       </c>
       <c r="P629" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="630" spans="1:16">
@@ -33788,7 +33791,7 @@
         <v>0</v>
       </c>
       <c r="P630" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="631" spans="1:16">
@@ -33838,7 +33841,7 @@
         <v>0</v>
       </c>
       <c r="P631" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="632" spans="1:16">
@@ -33888,7 +33891,7 @@
         <v>0</v>
       </c>
       <c r="P632" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="633" spans="1:16">
@@ -33938,7 +33941,7 @@
         <v>0</v>
       </c>
       <c r="P633" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="634" spans="1:16">
@@ -33988,7 +33991,7 @@
         <v>0</v>
       </c>
       <c r="P634" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="635" spans="1:16">
@@ -34038,7 +34041,7 @@
         <v>0</v>
       </c>
       <c r="P635" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="636" spans="1:16">
@@ -34088,7 +34091,7 @@
         <v>0</v>
       </c>
       <c r="P636" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="637" spans="1:16">
@@ -34138,7 +34141,7 @@
         <v>0</v>
       </c>
       <c r="P637" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="638" spans="1:16">
@@ -34188,7 +34191,7 @@
         <v>0</v>
       </c>
       <c r="P638" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="639" spans="1:16">
@@ -34238,7 +34241,7 @@
         <v>1</v>
       </c>
       <c r="P639" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="640" spans="1:16">
@@ -34288,7 +34291,7 @@
         <v>0</v>
       </c>
       <c r="P640" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="641" spans="1:16">
@@ -34338,7 +34341,7 @@
         <v>0</v>
       </c>
       <c r="P641" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="642" spans="1:16">
@@ -34388,7 +34391,7 @@
         <v>0</v>
       </c>
       <c r="P642" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="643" spans="1:16">
@@ -34438,7 +34441,7 @@
         <v>0</v>
       </c>
       <c r="P643" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="644" spans="1:16">
@@ -34488,7 +34491,7 @@
         <v>0</v>
       </c>
       <c r="P644" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="645" spans="1:16">
@@ -34538,7 +34541,7 @@
         <v>0</v>
       </c>
       <c r="P645" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="646" spans="1:16">
@@ -34588,7 +34591,7 @@
         <v>0</v>
       </c>
       <c r="P646" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="647" spans="1:16">
@@ -34638,7 +34641,7 @@
         <v>0</v>
       </c>
       <c r="P647" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="648" spans="1:16">
@@ -34688,7 +34691,7 @@
         <v>0</v>
       </c>
       <c r="P648" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="649" spans="1:16">
@@ -34738,7 +34741,7 @@
         <v>1</v>
       </c>
       <c r="P649" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="650" spans="1:16">
@@ -34788,7 +34791,7 @@
         <v>1</v>
       </c>
       <c r="P650" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="651" spans="1:16">
@@ -34838,7 +34841,7 @@
         <v>1</v>
       </c>
       <c r="P651" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="652" spans="1:16">
@@ -35038,7 +35041,7 @@
         <v>1</v>
       </c>
       <c r="P655" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="656" spans="1:16">
@@ -35088,7 +35091,7 @@
         <v>1</v>
       </c>
       <c r="P656" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="657" spans="1:16">
@@ -35138,7 +35141,7 @@
         <v>1</v>
       </c>
       <c r="P657" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="658" spans="1:16">
@@ -35288,7 +35291,7 @@
         <v>1</v>
       </c>
       <c r="P660" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="661" spans="1:16">
@@ -35338,7 +35341,7 @@
         <v>1</v>
       </c>
       <c r="P661" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="662" spans="1:16">
@@ -35438,7 +35441,7 @@
         <v>1</v>
       </c>
       <c r="P663" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="664" spans="1:16">
@@ -35538,7 +35541,7 @@
         <v>1</v>
       </c>
       <c r="P665" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="666" spans="1:16">
@@ -35588,7 +35591,7 @@
         <v>1</v>
       </c>
       <c r="P666" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="667" spans="1:16">
@@ -35617,7 +35620,7 @@
         <v>6.64</v>
       </c>
       <c r="P667" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="668" spans="1:16">
@@ -35667,7 +35670,7 @@
         <v>1</v>
       </c>
       <c r="P668" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="669" spans="1:16">
@@ -35717,7 +35720,7 @@
         <v>0</v>
       </c>
       <c r="P669" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="670" spans="1:16">
@@ -35767,7 +35770,7 @@
         <v>1</v>
       </c>
       <c r="P670" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="671" spans="1:16">
@@ -35817,7 +35820,7 @@
         <v>0</v>
       </c>
       <c r="P671" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="672" spans="1:16">
@@ -35867,7 +35870,7 @@
         <v>1</v>
       </c>
       <c r="P672" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="673" spans="1:16">
@@ -35896,7 +35899,7 @@
         <v>6.64</v>
       </c>
       <c r="P673" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="674" spans="1:16">
@@ -35925,7 +35928,7 @@
         <v>6.38</v>
       </c>
       <c r="P674" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="675" spans="1:16">
@@ -35975,7 +35978,7 @@
         <v>1</v>
       </c>
       <c r="P675" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="676" spans="1:16">
@@ -36025,7 +36028,7 @@
         <v>0</v>
       </c>
       <c r="P676" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="677" spans="1:16">
@@ -36075,7 +36078,7 @@
         <v>0</v>
       </c>
       <c r="P677" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="678" spans="1:16">
@@ -36125,7 +36128,7 @@
         <v>1</v>
       </c>
       <c r="P678" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="679" spans="1:16">
@@ -36175,7 +36178,7 @@
         <v>0</v>
       </c>
       <c r="P679" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="680" spans="1:16">
@@ -36225,7 +36228,7 @@
         <v>0</v>
       </c>
       <c r="P680" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="681" spans="1:16">
@@ -36275,7 +36278,7 @@
         <v>1</v>
       </c>
       <c r="P681" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="682" spans="1:16">
@@ -36325,7 +36328,7 @@
         <v>0</v>
       </c>
       <c r="P682" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="683" spans="1:16">
@@ -36375,7 +36378,7 @@
         <v>0</v>
       </c>
       <c r="P683" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="684" spans="1:16">
@@ -36425,7 +36428,7 @@
         <v>1</v>
       </c>
       <c r="P684" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="685" spans="1:16">
@@ -36454,7 +36457,7 @@
         <v>6.64</v>
       </c>
       <c r="P685" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="686" spans="1:16">
@@ -36483,7 +36486,7 @@
         <v>6.38</v>
       </c>
       <c r="P686" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="687" spans="1:16">
@@ -36512,7 +36515,7 @@
         <v>6.21</v>
       </c>
       <c r="P687" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="688" spans="1:16">
@@ -36562,7 +36565,7 @@
         <v>1</v>
       </c>
       <c r="P688" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="689" spans="1:16">
@@ -36612,7 +36615,7 @@
         <v>0</v>
       </c>
       <c r="P689" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="690" spans="1:16">
@@ -36662,7 +36665,7 @@
         <v>0</v>
       </c>
       <c r="P690" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="691" spans="1:16">
@@ -36712,7 +36715,7 @@
         <v>0</v>
       </c>
       <c r="P691" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="692" spans="1:16">
@@ -36762,7 +36765,7 @@
         <v>1</v>
       </c>
       <c r="P692" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="693" spans="1:16">
@@ -36812,7 +36815,7 @@
         <v>0</v>
       </c>
       <c r="P693" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="694" spans="1:16">
@@ -36862,7 +36865,7 @@
         <v>0</v>
       </c>
       <c r="P694" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="695" spans="1:16">
@@ -36912,7 +36915,7 @@
         <v>0</v>
       </c>
       <c r="P695" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="696" spans="1:16">
@@ -36962,7 +36965,7 @@
         <v>1</v>
       </c>
       <c r="P696" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="697" spans="1:16">
@@ -37012,7 +37015,7 @@
         <v>0</v>
       </c>
       <c r="P697" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="698" spans="1:16">
@@ -37062,7 +37065,7 @@
         <v>0</v>
       </c>
       <c r="P698" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="699" spans="1:16">
@@ -37112,7 +37115,7 @@
         <v>0</v>
       </c>
       <c r="P699" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="700" spans="1:16">
@@ -37162,7 +37165,7 @@
         <v>1</v>
       </c>
       <c r="P700" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="701" spans="1:16">
@@ -37212,7 +37215,7 @@
         <v>0</v>
       </c>
       <c r="P701" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="702" spans="1:16">
@@ -37262,7 +37265,7 @@
         <v>0</v>
       </c>
       <c r="P702" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="703" spans="1:16">
@@ -37312,7 +37315,7 @@
         <v>0</v>
       </c>
       <c r="P703" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="704" spans="1:16">
@@ -37362,7 +37365,7 @@
         <v>1</v>
       </c>
       <c r="P704" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="705" spans="1:16">
@@ -37412,7 +37415,7 @@
         <v>0</v>
       </c>
       <c r="P705" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="706" spans="1:16">
@@ -37462,7 +37465,7 @@
         <v>0</v>
       </c>
       <c r="P706" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="707" spans="1:16">
@@ -37512,7 +37515,7 @@
         <v>1</v>
       </c>
       <c r="P707" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="708" spans="1:16">
@@ -37562,7 +37565,7 @@
         <v>0</v>
       </c>
       <c r="P708" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="709" spans="1:16">
@@ -37612,7 +37615,7 @@
         <v>0</v>
       </c>
       <c r="P709" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="710" spans="1:16">
@@ -37662,7 +37665,7 @@
         <v>0</v>
       </c>
       <c r="P710" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="711" spans="1:16">
@@ -37712,7 +37715,7 @@
         <v>1</v>
       </c>
       <c r="P711" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="712" spans="1:16">
@@ -37762,7 +37765,7 @@
         <v>0</v>
       </c>
       <c r="P712" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="713" spans="1:16">
@@ -37812,7 +37815,7 @@
         <v>0</v>
       </c>
       <c r="P713" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="714" spans="1:16">
@@ -37862,7 +37865,7 @@
         <v>0</v>
       </c>
       <c r="P714" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="715" spans="1:16">
@@ -37912,7 +37915,7 @@
         <v>1</v>
       </c>
       <c r="P715" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="716" spans="1:16">
@@ -37962,7 +37965,7 @@
         <v>0</v>
       </c>
       <c r="P716" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="717" spans="1:16">
@@ -38012,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="P717" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="718" spans="1:16">
@@ -38062,7 +38065,7 @@
         <v>1</v>
       </c>
       <c r="P718" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="719" spans="1:16">
@@ -38112,7 +38115,7 @@
         <v>0</v>
       </c>
       <c r="P719" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="720" spans="1:16">
@@ -38162,7 +38165,7 @@
         <v>1</v>
       </c>
       <c r="P720" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="721" spans="1:16">
@@ -38212,7 +38215,7 @@
         <v>0</v>
       </c>
       <c r="P721" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="722" spans="1:16">
@@ -38262,7 +38265,7 @@
         <v>1</v>
       </c>
       <c r="P722" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="723" spans="1:16">
@@ -38312,7 +38315,7 @@
         <v>0</v>
       </c>
       <c r="P723" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="724" spans="1:16">
@@ -38362,7 +38365,7 @@
         <v>0</v>
       </c>
       <c r="P724" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="725" spans="1:16">
@@ -38412,7 +38415,7 @@
         <v>1</v>
       </c>
       <c r="P725" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="726" spans="1:16">
@@ -38462,7 +38465,7 @@
         <v>0</v>
       </c>
       <c r="P726" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="727" spans="1:16">
@@ -38512,7 +38515,7 @@
         <v>0</v>
       </c>
       <c r="P727" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="728" spans="1:16">
@@ -38562,7 +38565,7 @@
         <v>1</v>
       </c>
       <c r="P728" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="729" spans="1:16">
@@ -38591,7 +38594,7 @@
         <v>6.3</v>
       </c>
       <c r="P729" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="730" spans="1:16">
@@ -38620,7 +38623,7 @@
         <v>6.17</v>
       </c>
       <c r="P730" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="731" spans="1:16">
@@ -38820,7 +38823,7 @@
         <v>1</v>
       </c>
       <c r="P734" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="735" spans="1:16">
@@ -38870,7 +38873,7 @@
         <v>0</v>
       </c>
       <c r="P735" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="736" spans="1:16">
@@ -38920,7 +38923,7 @@
         <v>0</v>
       </c>
       <c r="P736" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="737" spans="1:16">
@@ -38970,7 +38973,7 @@
         <v>0</v>
       </c>
       <c r="P737" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="738" spans="1:16">
@@ -39370,7 +39373,7 @@
         <v>1</v>
       </c>
       <c r="P745" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="746" spans="1:16">
@@ -39420,7 +39423,7 @@
         <v>0</v>
       </c>
       <c r="P746" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="747" spans="1:16">
@@ -39470,7 +39473,7 @@
         <v>0</v>
       </c>
       <c r="P747" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="748" spans="1:16">
@@ -39520,7 +39523,7 @@
         <v>1</v>
       </c>
       <c r="P748" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="749" spans="1:16">
@@ -39570,7 +39573,7 @@
         <v>0</v>
       </c>
       <c r="P749" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="750" spans="1:16">
@@ -39620,7 +39623,7 @@
         <v>0</v>
       </c>
       <c r="P750" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="751" spans="1:16">
@@ -39670,7 +39673,7 @@
         <v>1</v>
       </c>
       <c r="P751" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="752" spans="1:16">
@@ -39720,7 +39723,7 @@
         <v>0</v>
       </c>
       <c r="P752" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="753" spans="1:16">
@@ -39770,7 +39773,7 @@
         <v>0</v>
       </c>
       <c r="P753" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="754" spans="1:16">
@@ -39820,7 +39823,7 @@
         <v>1</v>
       </c>
       <c r="P754" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="755" spans="1:16">
@@ -39870,7 +39873,7 @@
         <v>0</v>
       </c>
       <c r="P755" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="756" spans="1:16">
@@ -39920,7 +39923,7 @@
         <v>0</v>
       </c>
       <c r="P756" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="757" spans="1:16">
@@ -39970,7 +39973,7 @@
         <v>0</v>
       </c>
       <c r="P757" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="758" spans="1:16">
@@ -40020,7 +40023,7 @@
         <v>1</v>
       </c>
       <c r="P758" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="759" spans="1:16">
@@ -40070,7 +40073,7 @@
         <v>0</v>
       </c>
       <c r="P759" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="760" spans="1:16">
@@ -40120,7 +40123,7 @@
         <v>0</v>
       </c>
       <c r="P760" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="761" spans="1:16">
@@ -40170,7 +40173,7 @@
         <v>1</v>
       </c>
       <c r="P761" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="762" spans="1:16">
@@ -40220,7 +40223,7 @@
         <v>0</v>
       </c>
       <c r="P762" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="763" spans="1:16">
@@ -40270,7 +40273,7 @@
         <v>0</v>
       </c>
       <c r="P763" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="764" spans="1:16">
@@ -40320,7 +40323,7 @@
         <v>1</v>
       </c>
       <c r="P764" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="765" spans="1:16">
@@ -40370,7 +40373,7 @@
         <v>0</v>
       </c>
       <c r="P765" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="766" spans="1:16">
@@ -40420,7 +40423,7 @@
         <v>0</v>
       </c>
       <c r="P766" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="767" spans="1:16">
@@ -40470,7 +40473,7 @@
         <v>0</v>
       </c>
       <c r="P767" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="768" spans="1:16">
@@ -40520,7 +40523,7 @@
         <v>0</v>
       </c>
       <c r="P768" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="769" spans="1:16">
@@ -40570,7 +40573,7 @@
         <v>1</v>
       </c>
       <c r="P769" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="770" spans="1:16">
@@ -40620,7 +40623,7 @@
         <v>0</v>
       </c>
       <c r="P770" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="771" spans="1:16">
@@ -40670,7 +40673,7 @@
         <v>0</v>
       </c>
       <c r="P771" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="772" spans="1:16">
@@ -40720,7 +40723,7 @@
         <v>0</v>
       </c>
       <c r="P772" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="773" spans="1:16">
@@ -40770,7 +40773,7 @@
         <v>0</v>
       </c>
       <c r="P773" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="774" spans="1:16">
@@ -40820,7 +40823,7 @@
         <v>1</v>
       </c>
       <c r="P774" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="775" spans="1:16">
@@ -40870,7 +40873,7 @@
         <v>0</v>
       </c>
       <c r="P775" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="776" spans="1:16">
@@ -40920,7 +40923,7 @@
         <v>0</v>
       </c>
       <c r="P776" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="777" spans="1:16">
@@ -40970,7 +40973,7 @@
         <v>0</v>
       </c>
       <c r="P777" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="778" spans="1:16">
@@ -41020,7 +41023,7 @@
         <v>1</v>
       </c>
       <c r="P778" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="779" spans="1:16">
@@ -41070,7 +41073,7 @@
         <v>0</v>
       </c>
       <c r="P779" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="780" spans="1:16">
@@ -41120,7 +41123,7 @@
         <v>0</v>
       </c>
       <c r="P780" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="781" spans="1:16">
@@ -41170,7 +41173,7 @@
         <v>0</v>
       </c>
       <c r="P781" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="782" spans="1:16">
@@ -41220,7 +41223,7 @@
         <v>1</v>
       </c>
       <c r="P782" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="783" spans="1:16">
@@ -41270,7 +41273,7 @@
         <v>0</v>
       </c>
       <c r="P783" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="784" spans="1:16">
@@ -41320,7 +41323,7 @@
         <v>1</v>
       </c>
       <c r="P784" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="785" spans="1:16">
@@ -41370,7 +41373,7 @@
         <v>0</v>
       </c>
       <c r="P785" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
     </row>
     <row r="786" spans="1:16">
@@ -41420,7 +41423,7 @@
         <v>1</v>
       </c>
       <c r="P786" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
     </row>
     <row r="787" spans="1:16">
@@ -41470,7 +41473,7 @@
         <v>1</v>
       </c>
       <c r="P787" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
     </row>
     <row r="788" spans="1:16">
@@ -41520,7 +41523,7 @@
         <v>1</v>
       </c>
       <c r="P788" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="789" spans="1:16">
@@ -41570,7 +41573,7 @@
         <v>1</v>
       </c>
       <c r="P789" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="790" spans="1:16">
@@ -41620,7 +41623,7 @@
         <v>1</v>
       </c>
       <c r="P790" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="791" spans="1:16">
@@ -41670,7 +41673,7 @@
         <v>1</v>
       </c>
       <c r="P791" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="792" spans="1:16">
@@ -41720,7 +41723,7 @@
         <v>1</v>
       </c>
       <c r="P792" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="793" spans="1:16">
@@ -41770,7 +41773,7 @@
         <v>1</v>
       </c>
       <c r="P793" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="794" spans="1:16">
@@ -41820,7 +41823,7 @@
         <v>1</v>
       </c>
       <c r="P794" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="795" spans="1:16">
@@ -41870,7 +41873,7 @@
         <v>1</v>
       </c>
       <c r="P795" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="796" spans="1:16">
@@ -41920,7 +41923,7 @@
         <v>1</v>
       </c>
       <c r="P796" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="797" spans="1:16">
@@ -41970,7 +41973,7 @@
         <v>1</v>
       </c>
       <c r="P797" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="798" spans="1:16">
@@ -42020,7 +42023,7 @@
         <v>1</v>
       </c>
       <c r="P798" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="799" spans="1:16">
@@ -42070,7 +42073,7 @@
         <v>1</v>
       </c>
       <c r="P799" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="800" spans="1:16">
@@ -42120,7 +42123,7 @@
         <v>1</v>
       </c>
       <c r="P800" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="801" spans="1:16">
@@ -42170,7 +42173,7 @@
         <v>1</v>
       </c>
       <c r="P801" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="802" spans="1:16">
@@ -42220,7 +42223,7 @@
         <v>1</v>
       </c>
       <c r="P802" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="803" spans="1:16">
@@ -42270,7 +42273,7 @@
         <v>1</v>
       </c>
       <c r="P803" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="804" spans="1:16">
@@ -42320,7 +42323,7 @@
         <v>1</v>
       </c>
       <c r="P804" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="805" spans="1:16">
@@ -42370,7 +42373,7 @@
         <v>1</v>
       </c>
       <c r="P805" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="806" spans="1:16">
@@ -42420,7 +42423,7 @@
         <v>1</v>
       </c>
       <c r="P806" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="807" spans="1:16">
@@ -42470,7 +42473,7 @@
         <v>1</v>
       </c>
       <c r="P807" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="808" spans="1:16">
@@ -42520,7 +42523,7 @@
         <v>1</v>
       </c>
       <c r="P808" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="809" spans="1:16">
@@ -42570,7 +42573,7 @@
         <v>1</v>
       </c>
       <c r="P809" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="810" spans="1:16">
@@ -42620,7 +42623,7 @@
         <v>1</v>
       </c>
       <c r="P810" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
     </row>
     <row r="811" spans="1:16">
@@ -42670,7 +42673,7 @@
         <v>1</v>
       </c>
       <c r="P811" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="812" spans="1:16">
@@ -42720,7 +42723,7 @@
         <v>1</v>
       </c>
       <c r="P812" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
     </row>
     <row r="813" spans="1:16">
@@ -42920,7 +42923,7 @@
         <v>1</v>
       </c>
       <c r="P816" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="817" spans="1:16">
@@ -42970,7 +42973,7 @@
         <v>1</v>
       </c>
       <c r="P817" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="818" spans="1:16">
@@ -43020,7 +43023,7 @@
         <v>1</v>
       </c>
       <c r="P818" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="819" spans="1:16">
@@ -43070,7 +43073,7 @@
         <v>1</v>
       </c>
       <c r="P819" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
     </row>
     <row r="820" spans="1:16">
@@ -43120,7 +43123,7 @@
         <v>1</v>
       </c>
       <c r="P820" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="821" spans="1:16">
@@ -43170,7 +43173,7 @@
         <v>0</v>
       </c>
       <c r="P821" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="822" spans="1:16">
@@ -43220,7 +43223,7 @@
         <v>0</v>
       </c>
       <c r="P822" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
     </row>
     <row r="823" spans="1:16">
@@ -43670,7 +43673,7 @@
         <v>1</v>
       </c>
       <c r="P831" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="832" spans="1:16">
@@ -43720,7 +43723,7 @@
         <v>1</v>
       </c>
       <c r="P832" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="833" spans="1:16">
@@ -43770,7 +43773,7 @@
         <v>1</v>
       </c>
       <c r="P833" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="834" spans="1:16">
@@ -43820,7 +43823,7 @@
         <v>1</v>
       </c>
       <c r="P834" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="835" spans="1:16">
@@ -43849,7 +43852,7 @@
         <v>5.63</v>
       </c>
       <c r="P835" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="836" spans="1:16">
@@ -43899,7 +43902,7 @@
         <v>1</v>
       </c>
       <c r="P836" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="837" spans="1:16">
@@ -43949,7 +43952,7 @@
         <v>1</v>
       </c>
       <c r="P837" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="838" spans="1:16">
@@ -43999,7 +44002,7 @@
         <v>1</v>
       </c>
       <c r="P838" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="839" spans="1:16">
@@ -44049,7 +44052,7 @@
         <v>1</v>
       </c>
       <c r="P839" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="840" spans="1:16">
@@ -44099,7 +44102,7 @@
         <v>0</v>
       </c>
       <c r="P840" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
     </row>
     <row r="841" spans="1:16">
@@ -44299,7 +44302,7 @@
         <v>1</v>
       </c>
       <c r="P844" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="845" spans="1:16">
@@ -44349,7 +44352,7 @@
         <v>1</v>
       </c>
       <c r="P845" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="846" spans="1:16">
@@ -44399,7 +44402,7 @@
         <v>0</v>
       </c>
       <c r="P846" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
     </row>
     <row r="847" spans="1:16">
@@ -44449,7 +44452,7 @@
         <v>1</v>
       </c>
       <c r="P847" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="848" spans="1:16">
@@ -44499,7 +44502,7 @@
         <v>1</v>
       </c>
       <c r="P848" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="849" spans="1:16">
@@ -44549,7 +44552,7 @@
         <v>0</v>
       </c>
       <c r="P849" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
     </row>
     <row r="850" spans="1:16">
@@ -44599,7 +44602,7 @@
         <v>1</v>
       </c>
       <c r="P850" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="851" spans="1:16">
@@ -44649,7 +44652,7 @@
         <v>1</v>
       </c>
       <c r="P851" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="852" spans="1:16">
@@ -44699,7 +44702,7 @@
         <v>0</v>
       </c>
       <c r="P852" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
     </row>
     <row r="853" spans="1:16">
@@ -44749,7 +44752,7 @@
         <v>1</v>
       </c>
       <c r="P853" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="854" spans="1:16">
@@ -44799,7 +44802,7 @@
         <v>1</v>
       </c>
       <c r="P854" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="855" spans="1:16">
@@ -44849,7 +44852,7 @@
         <v>1</v>
       </c>
       <c r="P855" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="856" spans="1:16">
@@ -44899,7 +44902,7 @@
         <v>0</v>
       </c>
       <c r="P856" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
     </row>
     <row r="857" spans="1:16">
@@ -44949,7 +44952,7 @@
         <v>1</v>
       </c>
       <c r="P857" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="858" spans="1:16">
@@ -44999,7 +45002,7 @@
         <v>1</v>
       </c>
       <c r="P858" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="859" spans="1:16">
@@ -45049,7 +45052,7 @@
         <v>1</v>
       </c>
       <c r="P859" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="860" spans="1:16">
@@ -45099,7 +45102,7 @@
         <v>0</v>
       </c>
       <c r="P860" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
     </row>
     <row r="861" spans="1:16">
@@ -45299,7 +45302,7 @@
         <v>1</v>
       </c>
       <c r="P864" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="865" spans="1:16">
@@ -45349,7 +45352,7 @@
         <v>1</v>
       </c>
       <c r="P865" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="866" spans="1:16">
@@ -45399,7 +45402,7 @@
         <v>1</v>
       </c>
       <c r="P866" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
     </row>
     <row r="867" spans="1:16">
@@ -45449,7 +45452,7 @@
         <v>1</v>
       </c>
       <c r="P867" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="868" spans="1:16">
@@ -45499,7 +45502,7 @@
         <v>1</v>
       </c>
       <c r="P868" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="869" spans="1:16">
@@ -45549,7 +45552,7 @@
         <v>1</v>
       </c>
       <c r="P869" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
     </row>
     <row r="870" spans="1:16">
@@ -45599,7 +45602,7 @@
         <v>1</v>
       </c>
       <c r="P870" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="871" spans="1:16">
@@ -45649,7 +45652,7 @@
         <v>1</v>
       </c>
       <c r="P871" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="872" spans="1:16">
@@ -45699,7 +45702,7 @@
         <v>1</v>
       </c>
       <c r="P872" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="873" spans="1:16">
@@ -45749,7 +45752,7 @@
         <v>1</v>
       </c>
       <c r="P873" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="874" spans="1:16">
@@ -45799,7 +45802,7 @@
         <v>1</v>
       </c>
       <c r="P874" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
     </row>
     <row r="875" spans="1:16">
@@ -45849,7 +45852,7 @@
         <v>0</v>
       </c>
       <c r="P875" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="876" spans="1:16">
@@ -45899,7 +45902,7 @@
         <v>0</v>
       </c>
       <c r="P876" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="877" spans="1:16">
@@ -45949,7 +45952,7 @@
         <v>0</v>
       </c>
       <c r="P877" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
     </row>
     <row r="878" spans="1:16">
@@ -46099,7 +46102,7 @@
         <v>0</v>
       </c>
       <c r="P880" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
     </row>
     <row r="881" spans="1:16">
@@ -46149,7 +46152,7 @@
         <v>0</v>
       </c>
       <c r="P881" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
     </row>
     <row r="882" spans="1:16">
@@ -46199,7 +46202,7 @@
         <v>0</v>
       </c>
       <c r="P882" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
     </row>
     <row r="883" spans="1:16">
@@ -46249,7 +46252,7 @@
         <v>0</v>
       </c>
       <c r="P883" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
     </row>
     <row r="884" spans="1:16">
@@ -46299,7 +46302,7 @@
         <v>0</v>
       </c>
       <c r="P884" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="885" spans="1:16">
@@ -46328,7 +46331,7 @@
         <v>5.6</v>
       </c>
       <c r="P885" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
     </row>
     <row r="886" spans="1:16">
@@ -46378,7 +46381,7 @@
         <v>0</v>
       </c>
       <c r="P886" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
     </row>
     <row r="887" spans="1:16">
@@ -46578,7 +46581,7 @@
         <v>1</v>
       </c>
       <c r="P890" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="891" spans="1:16">
@@ -46628,7 +46631,7 @@
         <v>1</v>
       </c>
       <c r="P891" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="892" spans="1:16">
@@ -46678,7 +46681,7 @@
         <v>1</v>
       </c>
       <c r="P892" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
     </row>
     <row r="893" spans="1:16">
@@ -46728,7 +46731,7 @@
         <v>1</v>
       </c>
       <c r="P893" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="894" spans="1:16">
@@ -46778,7 +46781,7 @@
         <v>1</v>
       </c>
       <c r="P894" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="895" spans="1:16">
@@ -46828,7 +46831,7 @@
         <v>1</v>
       </c>
       <c r="P895" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="896" spans="1:16">
@@ -46878,7 +46881,7 @@
         <v>1</v>
       </c>
       <c r="P896" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
     </row>
     <row r="897" spans="1:16">
@@ -46928,7 +46931,7 @@
         <v>1</v>
       </c>
       <c r="P897" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
     </row>
     <row r="898" spans="1:16">
@@ -46978,7 +46981,7 @@
         <v>1</v>
       </c>
       <c r="P898" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="899" spans="1:16">
@@ -47028,7 +47031,7 @@
         <v>1</v>
       </c>
       <c r="P899" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
     </row>
     <row r="900" spans="1:16">
@@ -47078,7 +47081,7 @@
         <v>1</v>
       </c>
       <c r="P900" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="901" spans="1:16">
@@ -47128,7 +47131,7 @@
         <v>1</v>
       </c>
       <c r="P901" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
     </row>
     <row r="902" spans="1:16">
@@ -47278,7 +47281,7 @@
         <v>1</v>
       </c>
       <c r="P904" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="905" spans="1:16">
@@ -47328,7 +47331,7 @@
         <v>1</v>
       </c>
       <c r="P905" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="906" spans="1:16">
@@ -47378,7 +47381,7 @@
         <v>1</v>
       </c>
       <c r="P906" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="907" spans="1:16">
@@ -47428,7 +47431,7 @@
         <v>1</v>
       </c>
       <c r="P907" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="908" spans="1:16">
@@ -47478,7 +47481,7 @@
         <v>1</v>
       </c>
       <c r="P908" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="909" spans="1:16">
@@ -47528,7 +47531,7 @@
         <v>1</v>
       </c>
       <c r="P909" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="910" spans="1:16">
@@ -47578,7 +47581,7 @@
         <v>1</v>
       </c>
       <c r="P910" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="911" spans="1:16">
@@ -47628,7 +47631,7 @@
         <v>1</v>
       </c>
       <c r="P911" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="912" spans="1:16">
@@ -47678,7 +47681,7 @@
         <v>1</v>
       </c>
       <c r="P912" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
     </row>
     <row r="913" spans="1:16">
@@ -47728,7 +47731,7 @@
         <v>1</v>
       </c>
       <c r="P913" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="914" spans="1:16">
@@ -47778,7 +47781,7 @@
         <v>1</v>
       </c>
       <c r="P914" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="915" spans="1:16">
@@ -47828,7 +47831,7 @@
         <v>1</v>
       </c>
       <c r="P915" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="916" spans="1:16">
@@ -47878,7 +47881,7 @@
         <v>1</v>
       </c>
       <c r="P916" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="917" spans="1:16">
@@ -47928,7 +47931,7 @@
         <v>1</v>
       </c>
       <c r="P917" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="918" spans="1:16">
@@ -47978,7 +47981,7 @@
         <v>1</v>
       </c>
       <c r="P918" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="919" spans="1:16">
@@ -48028,7 +48031,7 @@
         <v>1</v>
       </c>
       <c r="P919" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="920" spans="1:16">
@@ -48078,7 +48081,7 @@
         <v>1</v>
       </c>
       <c r="P920" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="921" spans="1:16">
@@ -48128,7 +48131,7 @@
         <v>1</v>
       </c>
       <c r="P921" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="922" spans="1:16">
@@ -48178,7 +48181,7 @@
         <v>1</v>
       </c>
       <c r="P922" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="923" spans="1:16">
@@ -48228,7 +48231,7 @@
         <v>1</v>
       </c>
       <c r="P923" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="924" spans="1:16">
@@ -48278,7 +48281,7 @@
         <v>1</v>
       </c>
       <c r="P924" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
     </row>
     <row r="925" spans="1:16">
@@ -48328,7 +48331,7 @@
         <v>1</v>
       </c>
       <c r="P925" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="926" spans="1:16">
@@ -48378,7 +48381,7 @@
         <v>1</v>
       </c>
       <c r="P926" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="927" spans="1:16">
@@ -48428,7 +48431,7 @@
         <v>1</v>
       </c>
       <c r="P927" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="928" spans="1:16">
@@ -48478,7 +48481,7 @@
         <v>1</v>
       </c>
       <c r="P928" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="929" spans="1:16">
@@ -48528,7 +48531,7 @@
         <v>1</v>
       </c>
       <c r="P929" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="930" spans="1:16">
@@ -48578,7 +48581,7 @@
         <v>1</v>
       </c>
       <c r="P930" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="931" spans="1:16">
@@ -48628,7 +48631,7 @@
         <v>1</v>
       </c>
       <c r="P931" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="932" spans="1:16">
@@ -48678,7 +48681,7 @@
         <v>1</v>
       </c>
       <c r="P932" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="933" spans="1:16">
@@ -48728,7 +48731,7 @@
         <v>1</v>
       </c>
       <c r="P933" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="934" spans="1:16">
@@ -48778,7 +48781,7 @@
         <v>1</v>
       </c>
       <c r="P934" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="935" spans="1:16">
@@ -48828,7 +48831,7 @@
         <v>1</v>
       </c>
       <c r="P935" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="936" spans="1:16">
@@ -48878,7 +48881,7 @@
         <v>1</v>
       </c>
       <c r="P936" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="937" spans="1:16">
@@ -48928,7 +48931,7 @@
         <v>1</v>
       </c>
       <c r="P937" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="938" spans="1:16">
@@ -48978,7 +48981,7 @@
         <v>1</v>
       </c>
       <c r="P938" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="939" spans="1:16">
@@ -49028,7 +49031,7 @@
         <v>1</v>
       </c>
       <c r="P939" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="940" spans="1:16">
@@ -49078,7 +49081,7 @@
         <v>1</v>
       </c>
       <c r="P940" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="941" spans="1:16">
@@ -49128,7 +49131,7 @@
         <v>1</v>
       </c>
       <c r="P941" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="942" spans="1:16">
@@ -49178,7 +49181,7 @@
         <v>1</v>
       </c>
       <c r="P942" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="943" spans="1:16">
@@ -49228,7 +49231,7 @@
         <v>1</v>
       </c>
       <c r="P943" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="944" spans="1:16">
@@ -49278,7 +49281,7 @@
         <v>1</v>
       </c>
       <c r="P944" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
     </row>
     <row r="945" spans="1:16">
@@ -49328,7 +49331,7 @@
         <v>1</v>
       </c>
       <c r="P945" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="946" spans="1:16">
@@ -49378,7 +49381,7 @@
         <v>1</v>
       </c>
       <c r="P946" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="947" spans="1:16">
@@ -49428,7 +49431,7 @@
         <v>1</v>
       </c>
       <c r="P947" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="948" spans="1:16">
@@ -49478,7 +49481,7 @@
         <v>1</v>
       </c>
       <c r="P948" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="949" spans="1:16">
@@ -49528,7 +49531,7 @@
         <v>1</v>
       </c>
       <c r="P949" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="950" spans="1:16">
@@ -49578,7 +49581,7 @@
         <v>1</v>
       </c>
       <c r="P950" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="951" spans="1:16">
@@ -49628,7 +49631,7 @@
         <v>1</v>
       </c>
       <c r="P951" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="952" spans="1:16">
@@ -49678,7 +49681,7 @@
         <v>1</v>
       </c>
       <c r="P952" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="953" spans="1:16">
@@ -49728,7 +49731,7 @@
         <v>1</v>
       </c>
       <c r="P953" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="954" spans="1:16">
@@ -49778,7 +49781,7 @@
         <v>1</v>
       </c>
       <c r="P954" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
     </row>
     <row r="955" spans="1:16">
@@ -49786,49 +49789,49 @@
         <v>0</v>
       </c>
       <c r="B955" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C955">
-        <v>2.431508980050069</v>
+        <v>3.532936083572772</v>
       </c>
       <c r="D955" t="s">
         <v>461</v>
       </c>
       <c r="E955">
-        <v>3.11269056272443</v>
+        <v>2.843355524083167</v>
       </c>
       <c r="F955">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G955">
-        <v>0.008748491019949931</v>
+        <v>0.00842706391642723</v>
       </c>
       <c r="H955">
-        <v>0.008767309437275569</v>
+        <v>0.008436644475916832</v>
       </c>
       <c r="I955">
-        <v>0.6811815826743612</v>
+        <v>0.6895805594896047</v>
       </c>
       <c r="J955">
         <v>0.06132992271747439</v>
       </c>
       <c r="K955">
-        <v>51.5</v>
+        <v>39.9</v>
       </c>
       <c r="L955">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
       <c r="M955">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N955">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O955">
         <v>1</v>
       </c>
       <c r="P955" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="956" spans="1:16">
@@ -49836,13 +49839,13 @@
         <v>1</v>
       </c>
       <c r="B956" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C956">
-        <v>3.532936083572772</v>
+        <v>3.470017927480011</v>
       </c>
       <c r="D956" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E956">
         <v>2.843355524083167</v>
@@ -49851,22 +49854,22 @@
         <v>-1</v>
       </c>
       <c r="G956">
-        <v>0.00842706391642723</v>
+        <v>0.00890998207251999</v>
       </c>
       <c r="H956">
         <v>0.008436644475916832</v>
       </c>
       <c r="I956">
-        <v>0.6895805594896047</v>
+        <v>0.6266624033968435</v>
       </c>
       <c r="J956">
         <v>0.06132992271747439</v>
       </c>
       <c r="K956">
-        <v>39.9</v>
+        <v>44.35</v>
       </c>
       <c r="L956">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M956">
         <v>45.6</v>
@@ -49878,121 +49881,121 @@
         <v>1</v>
       </c>
       <c r="P956" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="957" spans="1:16">
       <c r="A957" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B957" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C957">
-        <v>3.470017927480011</v>
+        <v>2.046214498970668</v>
       </c>
       <c r="D957" t="s">
         <v>462</v>
       </c>
       <c r="E957">
-        <v>2.843355524083167</v>
+        <v>2.767795891311607</v>
       </c>
       <c r="F957">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G957">
-        <v>0.00890998207251999</v>
+        <v>0.009133785501029331</v>
       </c>
       <c r="H957">
-        <v>0.008436644475916832</v>
+        <v>0.009112204108688392</v>
       </c>
       <c r="I957">
-        <v>0.6266624033968435</v>
+        <v>0.7215813923409389</v>
       </c>
       <c r="J957">
-        <v>0.06132992271747439</v>
+        <v>0.06881136895202586</v>
       </c>
       <c r="K957">
-        <v>44.35</v>
+        <v>51.5</v>
       </c>
       <c r="L957">
-        <v>6.19</v>
+        <v>5.59</v>
       </c>
       <c r="M957">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="N957">
-        <v>5.64</v>
+        <v>5.94</v>
       </c>
       <c r="O957">
         <v>1</v>
       </c>
       <c r="P957" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="958" spans="1:16">
       <c r="A958" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B958" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C958">
-        <v>2.046214498970668</v>
+        <v>3.234426378814169</v>
       </c>
       <c r="D958" t="s">
         <v>461</v>
       </c>
       <c r="E958">
-        <v>2.767795891311607</v>
+        <v>2.502201575787621</v>
       </c>
       <c r="F958">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G958">
-        <v>0.009133785501029331</v>
+        <v>0.008725573621185832</v>
       </c>
       <c r="H958">
-        <v>0.009112204108688392</v>
+        <v>0.008777798424212379</v>
       </c>
       <c r="I958">
-        <v>0.7215813923409389</v>
+        <v>0.7322248030265484</v>
       </c>
       <c r="J958">
         <v>0.06881136895202586</v>
       </c>
       <c r="K958">
-        <v>51.5</v>
+        <v>39.9</v>
       </c>
       <c r="L958">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
       <c r="M958">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N958">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O958">
         <v>1</v>
       </c>
       <c r="P958" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="959" spans="1:16">
       <c r="A959" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B959" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C959">
-        <v>3.234426378814169</v>
+        <v>3.138215786977653</v>
       </c>
       <c r="D959" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E959">
         <v>2.502201575787621</v>
@@ -50001,22 +50004,22 @@
         <v>-1</v>
       </c>
       <c r="G959">
-        <v>0.008725573621185832</v>
+        <v>0.009241784213022347</v>
       </c>
       <c r="H959">
         <v>0.008777798424212379</v>
       </c>
       <c r="I959">
-        <v>0.7322248030265484</v>
+        <v>0.6360142111900329</v>
       </c>
       <c r="J959">
         <v>0.06881136895202586</v>
       </c>
       <c r="K959">
-        <v>39.9</v>
+        <v>44.35</v>
       </c>
       <c r="L959">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M959">
         <v>45.6</v>
@@ -50028,121 +50031,121 @@
         <v>1</v>
       </c>
       <c r="P959" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
     </row>
     <row r="960" spans="1:16">
       <c r="A960" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B960" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C960">
-        <v>3.138215786977653</v>
+        <v>2.025162321012973</v>
       </c>
       <c r="D960" t="s">
         <v>462</v>
       </c>
       <c r="E960">
-        <v>2.502201575787621</v>
+        <v>2.748951126188311</v>
       </c>
       <c r="F960">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G960">
-        <v>0.009241784213022347</v>
+        <v>0.009154837678987027</v>
       </c>
       <c r="H960">
-        <v>0.008777798424212379</v>
+        <v>0.009131048873811687</v>
       </c>
       <c r="I960">
-        <v>0.6360142111900329</v>
+        <v>0.7237888051753383</v>
       </c>
       <c r="J960">
-        <v>0.06881136895202586</v>
+        <v>0.06922014910654421</v>
       </c>
       <c r="K960">
-        <v>44.35</v>
+        <v>51.5</v>
       </c>
       <c r="L960">
-        <v>6.19</v>
+        <v>5.59</v>
       </c>
       <c r="M960">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="N960">
-        <v>5.64</v>
+        <v>5.94</v>
       </c>
       <c r="O960">
         <v>1</v>
       </c>
       <c r="P960" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
     </row>
     <row r="961" spans="1:16">
       <c r="A961" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B961" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C961">
-        <v>2.025162321012973</v>
+        <v>3.218116050648887</v>
       </c>
       <c r="D961" t="s">
         <v>461</v>
       </c>
       <c r="E961">
-        <v>2.748951126188311</v>
+        <v>2.483561200741584</v>
       </c>
       <c r="F961">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G961">
-        <v>0.009154837678987027</v>
+        <v>0.008741883949351116</v>
       </c>
       <c r="H961">
-        <v>0.009131048873811687</v>
+        <v>0.008796438799258417</v>
       </c>
       <c r="I961">
-        <v>0.7237888051753383</v>
+        <v>0.7345548499073029</v>
       </c>
       <c r="J961">
         <v>0.06922014910654421</v>
       </c>
       <c r="K961">
-        <v>51.5</v>
+        <v>39.9</v>
       </c>
       <c r="L961">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
       <c r="M961">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N961">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O961">
         <v>1</v>
       </c>
       <c r="P961" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="962" spans="1:16">
       <c r="A962" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B962" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C962">
-        <v>3.218116050648887</v>
+        <v>3.120086387124764</v>
       </c>
       <c r="D962" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E962">
         <v>2.483561200741584</v>
@@ -50151,22 +50154,22 @@
         <v>-1</v>
       </c>
       <c r="G962">
-        <v>0.008741883949351116</v>
+        <v>0.009259913612875236</v>
       </c>
       <c r="H962">
         <v>0.008796438799258417</v>
       </c>
       <c r="I962">
-        <v>0.7345548499073029</v>
+        <v>0.6365251863831807</v>
       </c>
       <c r="J962">
         <v>0.06922014910654421</v>
       </c>
       <c r="K962">
-        <v>39.9</v>
+        <v>44.35</v>
       </c>
       <c r="L962">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M962">
         <v>45.6</v>
@@ -50178,121 +50181,121 @@
         <v>1</v>
       </c>
       <c r="P962" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="963" spans="1:16">
       <c r="A963" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B963" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C963">
-        <v>3.120086387124764</v>
+        <v>2.047715219225316</v>
       </c>
       <c r="D963" t="s">
         <v>462</v>
       </c>
       <c r="E963">
-        <v>2.483561200741584</v>
+        <v>2.769139254491011</v>
       </c>
       <c r="F963">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G963">
-        <v>0.009259913612875236</v>
+        <v>0.009132284780774682</v>
       </c>
       <c r="H963">
-        <v>0.008796438799258417</v>
+        <v>0.009110860745508988</v>
       </c>
       <c r="I963">
-        <v>0.6365251863831807</v>
+        <v>0.7214240352656947</v>
       </c>
       <c r="J963">
-        <v>0.06922014910654421</v>
+        <v>0.06878222875290647</v>
       </c>
       <c r="K963">
-        <v>44.35</v>
+        <v>51.5</v>
       </c>
       <c r="L963">
-        <v>6.19</v>
+        <v>5.59</v>
       </c>
       <c r="M963">
-        <v>45.6</v>
+        <v>46.1</v>
       </c>
       <c r="N963">
-        <v>5.64</v>
+        <v>5.94</v>
       </c>
       <c r="O963">
         <v>1</v>
       </c>
       <c r="P963" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
     </row>
     <row r="964" spans="1:16">
       <c r="A964" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B964" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C964">
-        <v>2.047715219225316</v>
+        <v>3.235589072759032</v>
       </c>
       <c r="D964" t="s">
         <v>461</v>
       </c>
       <c r="E964">
-        <v>2.769139254491011</v>
+        <v>2.503530368867464</v>
       </c>
       <c r="F964">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G964">
-        <v>0.009132284780774682</v>
+        <v>0.00872441092724097</v>
       </c>
       <c r="H964">
-        <v>0.009110860745508988</v>
+        <v>0.008776469631132535</v>
       </c>
       <c r="I964">
-        <v>0.7214240352656947</v>
+        <v>0.732058703891568</v>
       </c>
       <c r="J964">
         <v>0.06878222875290647</v>
       </c>
       <c r="K964">
-        <v>51.5</v>
+        <v>39.9</v>
       </c>
       <c r="L964">
-        <v>5.59</v>
+        <v>5.98</v>
       </c>
       <c r="M964">
-        <v>46.1</v>
+        <v>45.6</v>
       </c>
       <c r="N964">
-        <v>5.94</v>
+        <v>5.64</v>
       </c>
       <c r="O964">
         <v>1</v>
       </c>
       <c r="P964" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="965" spans="1:16">
       <c r="A965" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B965" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C965">
-        <v>3.235589072759032</v>
+        <v>3.139508154808598</v>
       </c>
       <c r="D965" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="E965">
         <v>2.503530368867464</v>
@@ -50301,22 +50304,22 @@
         <v>-1</v>
       </c>
       <c r="G965">
-        <v>0.00872441092724097</v>
+        <v>0.009240491845191403</v>
       </c>
       <c r="H965">
         <v>0.008776469631132535</v>
       </c>
       <c r="I965">
-        <v>0.732058703891568</v>
+        <v>0.635977785941134</v>
       </c>
       <c r="J965">
         <v>0.06878222875290647</v>
       </c>
       <c r="K965">
-        <v>39.9</v>
+        <v>44.35</v>
       </c>
       <c r="L965">
-        <v>5.98</v>
+        <v>6.19</v>
       </c>
       <c r="M965">
         <v>45.6</v>
@@ -50328,39 +50331,39 @@
         <v>1</v>
       </c>
       <c r="P965" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
     </row>
     <row r="966" spans="1:16">
       <c r="A966" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B966" t="s">
         <v>221</v>
       </c>
       <c r="C966">
-        <v>3.139508154808598</v>
+        <v>6.518598702106193</v>
       </c>
       <c r="D966" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="E966">
-        <v>2.503530368867464</v>
+        <v>5.980075663656012</v>
       </c>
       <c r="F966">
         <v>-1</v>
       </c>
       <c r="G966">
-        <v>0.009240491845191403</v>
+        <v>0.005861401297893808</v>
       </c>
       <c r="H966">
-        <v>0.008776469631132535</v>
+        <v>0.005359924336343988</v>
       </c>
       <c r="I966">
-        <v>0.635977785941134</v>
+        <v>0.5385230384501805</v>
       </c>
       <c r="J966">
-        <v>0.06878222875290647</v>
+        <v>-0.007409215380071977</v>
       </c>
       <c r="K966">
         <v>44.35</v>
@@ -50369,116 +50372,116 @@
         <v>6.19</v>
       </c>
       <c r="M966">
-        <v>45.6</v>
+        <v>41.85</v>
       </c>
       <c r="N966">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="O966">
         <v>1</v>
       </c>
       <c r="P966" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
     </row>
     <row r="967" spans="1:16">
       <c r="A967" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B967" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C967">
-        <v>6.518598702106193</v>
+        <v>5.568223359810994</v>
       </c>
       <c r="D967" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E967">
-        <v>5.980075663656012</v>
+        <v>5.634155613641246</v>
       </c>
       <c r="F967">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G967">
-        <v>0.005861401297893808</v>
+        <v>0.004951776640189006</v>
       </c>
       <c r="H967">
-        <v>0.005359924336343988</v>
+        <v>0.004965844386358754</v>
       </c>
       <c r="I967">
-        <v>0.5385230384501805</v>
+        <v>0.06593225383025203</v>
       </c>
       <c r="J967">
         <v>-0.007409215380071977</v>
       </c>
       <c r="K967">
-        <v>44.35</v>
+        <v>41.6</v>
       </c>
       <c r="L967">
-        <v>6.19</v>
+        <v>5.26</v>
       </c>
       <c r="M967">
-        <v>41.85</v>
+        <v>45.1</v>
       </c>
       <c r="N967">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="O967">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P967" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="968" spans="1:16">
       <c r="A968" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B968" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C968">
-        <v>5.568223359810994</v>
+        <v>5.552298428270034</v>
       </c>
       <c r="D968" t="s">
-        <v>223</v>
+        <v>464</v>
       </c>
       <c r="E968">
-        <v>5.552298428270034</v>
+        <v>5.634155613641246</v>
       </c>
       <c r="F968">
         <v>1</v>
       </c>
       <c r="G968">
-        <v>0.004951776640189006</v>
+        <v>0.004927701571729967</v>
       </c>
       <c r="H968">
-        <v>0.004927701571729967</v>
+        <v>0.004965844386358754</v>
       </c>
       <c r="I968">
-        <v>-0.01592493154095997</v>
+        <v>0.081857185371212</v>
       </c>
       <c r="J968">
         <v>-0.007409215380071977</v>
       </c>
       <c r="K968">
-        <v>41.6</v>
+        <v>42.15</v>
       </c>
       <c r="L968">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="M968">
-        <v>42.15</v>
+        <v>45.1</v>
       </c>
       <c r="N968">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="O968">
         <v>0</v>
       </c>
       <c r="P968" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="969" spans="1:16">
@@ -50528,7 +50531,7 @@
         <v>1</v>
       </c>
       <c r="P969" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="970" spans="1:16">
@@ -50542,10 +50545,10 @@
         <v>6.011864008014902</v>
       </c>
       <c r="D970" t="s">
-        <v>223</v>
+        <v>464</v>
       </c>
       <c r="E970">
-        <v>6.001804517736253</v>
+        <v>6.115121797150771</v>
       </c>
       <c r="F970">
         <v>1</v>
@@ -50554,10 +50557,10 @@
         <v>0.004508135991985098</v>
       </c>
       <c r="H970">
-        <v>0.004478195482263748</v>
+        <v>0.004484878202849229</v>
       </c>
       <c r="I970">
-        <v>-0.01005949027864883</v>
+        <v>0.1032577891358688</v>
       </c>
       <c r="J970">
         <v>-0.01807365403881975</v>
@@ -50569,63 +50572,63 @@
         <v>5.26</v>
       </c>
       <c r="M970">
-        <v>42.15</v>
+        <v>45.1</v>
       </c>
       <c r="N970">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="O970">
         <v>0</v>
       </c>
       <c r="P970" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
     </row>
     <row r="971" spans="1:16">
       <c r="A971" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B971" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C971">
-        <v>7.158772656458988</v>
+        <v>6.001804517736253</v>
       </c>
       <c r="D971" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="E971">
-        <v>6.584163149330522</v>
+        <v>6.115121797150771</v>
       </c>
       <c r="F971">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="G971">
-        <v>0.005221227343541013</v>
+        <v>0.004478195482263748</v>
       </c>
       <c r="H971">
-        <v>0.004755836850669478</v>
+        <v>0.004484878202849229</v>
       </c>
       <c r="I971">
-        <v>0.574609507128466</v>
+        <v>0.1133172794145176</v>
       </c>
       <c r="J971">
-        <v>-0.02184380285138643</v>
+        <v>-0.01807365403881975</v>
       </c>
       <c r="K971">
-        <v>44.35</v>
+        <v>42.15</v>
       </c>
       <c r="L971">
-        <v>6.19</v>
+        <v>5.24</v>
       </c>
       <c r="M971">
-        <v>41.85</v>
+        <v>45.1</v>
       </c>
       <c r="N971">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="O971">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P971" t="s">
         <v>791</v>
@@ -50633,84 +50636,84 @@
     </row>
     <row r="972" spans="1:16">
       <c r="A972" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B972" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C972">
-        <v>6.168702198617676</v>
+        <v>7.158772656458988</v>
       </c>
       <c r="D972" t="s">
-        <v>223</v>
+        <v>463</v>
       </c>
       <c r="E972">
-        <v>6.160716290185938</v>
+        <v>6.584163149330522</v>
       </c>
       <c r="F972">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G972">
-        <v>0.004351297801382324</v>
+        <v>0.005221227343541013</v>
       </c>
       <c r="H972">
-        <v>0.004319283709814062</v>
+        <v>0.004755836850669478</v>
       </c>
       <c r="I972">
-        <v>-0.007985908431737521</v>
+        <v>0.574609507128466</v>
       </c>
       <c r="J972">
         <v>-0.02184380285138643</v>
       </c>
       <c r="K972">
-        <v>41.6</v>
+        <v>44.35</v>
       </c>
       <c r="L972">
-        <v>5.26</v>
+        <v>6.19</v>
       </c>
       <c r="M972">
-        <v>42.15</v>
+        <v>41.85</v>
       </c>
       <c r="N972">
-        <v>5.24</v>
+        <v>5.67</v>
       </c>
       <c r="O972">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P972" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="973" spans="1:16">
       <c r="A973" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B973" t="s">
         <v>222</v>
       </c>
       <c r="C973">
-        <v>6.188403991653797</v>
+        <v>6.168702198617676</v>
       </c>
       <c r="D973" t="s">
-        <v>223</v>
+        <v>464</v>
       </c>
       <c r="E973">
-        <v>6.180678563658835</v>
+        <v>6.285155508597528</v>
       </c>
       <c r="F973">
         <v>1</v>
       </c>
       <c r="G973">
-        <v>0.004331596008346203</v>
+        <v>0.004351297801382324</v>
       </c>
       <c r="H973">
-        <v>0.004299321436341166</v>
+        <v>0.004314844491402472</v>
       </c>
       <c r="I973">
-        <v>-0.007725427994961898</v>
+        <v>0.1164533099798524</v>
       </c>
       <c r="J973">
-        <v>-0.02231740364552396</v>
+        <v>-0.02184380285138643</v>
       </c>
       <c r="K973">
         <v>41.6</v>
@@ -50719,60 +50722,60 @@
         <v>5.26</v>
       </c>
       <c r="M973">
-        <v>42.15</v>
+        <v>45.1</v>
       </c>
       <c r="N973">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="O973">
         <v>0</v>
       </c>
       <c r="P973" t="s">
-        <v>221</v>
+        <v>792</v>
       </c>
     </row>
     <row r="974" spans="1:16">
       <c r="A974" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B974" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C974">
-        <v>6.158630136986302</v>
+        <v>6.160716290185938</v>
       </c>
       <c r="D974" t="s">
-        <v>223</v>
+        <v>464</v>
       </c>
       <c r="E974">
-        <v>6.150511064278188</v>
+        <v>6.285155508597528</v>
       </c>
       <c r="F974">
         <v>1</v>
       </c>
       <c r="G974">
-        <v>0.004361369863013698</v>
+        <v>0.004319283709814062</v>
       </c>
       <c r="H974">
-        <v>0.004329488935721813</v>
+        <v>0.004314844491402472</v>
       </c>
       <c r="I974">
-        <v>-0.008119072708113961</v>
+        <v>0.1244392184115899</v>
       </c>
       <c r="J974">
-        <v>-0.02160168598524764</v>
+        <v>-0.02184380285138643</v>
       </c>
       <c r="K974">
-        <v>41.6</v>
+        <v>42.15</v>
       </c>
       <c r="L974">
-        <v>5.26</v>
+        <v>5.24</v>
       </c>
       <c r="M974">
-        <v>42.15</v>
+        <v>45.1</v>
       </c>
       <c r="N974">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="O974">
         <v>0</v>
@@ -50789,16 +50792,28 @@
         <v>222</v>
       </c>
       <c r="C975">
-        <v>5.32829599901169</v>
+        <v>6.188403991653797</v>
+      </c>
+      <c r="D975" t="s">
+        <v>464</v>
+      </c>
+      <c r="E975">
+        <v>6.30651490441313</v>
       </c>
       <c r="F975">
         <v>1</v>
       </c>
       <c r="G975">
-        <v>0.005191704000988309</v>
+        <v>0.004331596008346203</v>
+      </c>
+      <c r="H975">
+        <v>0.00429348509558687</v>
+      </c>
+      <c r="I975">
+        <v>0.1181109127593336</v>
       </c>
       <c r="J975">
-        <v>-0.00164173074547332</v>
+        <v>-0.02231740364552396</v>
       </c>
       <c r="K975">
         <v>41.6</v>
@@ -50806,8 +50821,17 @@
       <c r="L975">
         <v>5.26</v>
       </c>
+      <c r="M975">
+        <v>45.1</v>
+      </c>
+      <c r="N975">
+        <v>5.3</v>
+      </c>
+      <c r="O975">
+        <v>0</v>
+      </c>
       <c r="P975" t="s">
-        <v>793</v>
+        <v>221</v>
       </c>
     </row>
     <row r="976" spans="1:16">
@@ -50818,16 +50842,28 @@
         <v>223</v>
       </c>
       <c r="C976">
-        <v>5.309198950921701</v>
+        <v>6.180678563658835</v>
+      </c>
+      <c r="D976" t="s">
+        <v>464</v>
+      </c>
+      <c r="E976">
+        <v>6.30651490441313</v>
       </c>
       <c r="F976">
         <v>1</v>
       </c>
       <c r="G976">
-        <v>0.0051708010490783</v>
+        <v>0.004299321436341166</v>
+      </c>
+      <c r="H976">
+        <v>0.00429348509558687</v>
+      </c>
+      <c r="I976">
+        <v>0.1258363407542955</v>
       </c>
       <c r="J976">
-        <v>-0.00164173074547332</v>
+        <v>-0.02231740364552396</v>
       </c>
       <c r="K976">
         <v>42.15</v>
@@ -50835,8 +50871,217 @@
       <c r="L976">
         <v>5.24</v>
       </c>
+      <c r="M976">
+        <v>45.1</v>
+      </c>
+      <c r="N976">
+        <v>5.3</v>
+      </c>
+      <c r="O976">
+        <v>0</v>
+      </c>
       <c r="P976" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="977" spans="1:16">
+      <c r="A977" s="1">
+        <v>0</v>
+      </c>
+      <c r="B977" t="s">
+        <v>222</v>
+      </c>
+      <c r="C977">
+        <v>6.158630136986302</v>
+      </c>
+      <c r="D977" t="s">
+        <v>464</v>
+      </c>
+      <c r="E977">
+        <v>6.274236037934668</v>
+      </c>
+      <c r="F977">
+        <v>1</v>
+      </c>
+      <c r="G977">
+        <v>0.004361369863013698</v>
+      </c>
+      <c r="H977">
+        <v>0.004325763962065332</v>
+      </c>
+      <c r="I977">
+        <v>0.1156059009483661</v>
+      </c>
+      <c r="J977">
+        <v>-0.02160168598524764</v>
+      </c>
+      <c r="K977">
+        <v>41.6</v>
+      </c>
+      <c r="L977">
+        <v>5.26</v>
+      </c>
+      <c r="M977">
+        <v>45.1</v>
+      </c>
+      <c r="N977">
+        <v>5.3</v>
+      </c>
+      <c r="O977">
+        <v>0</v>
+      </c>
+      <c r="P977" t="s">
         <v>793</v>
+      </c>
+    </row>
+    <row r="978" spans="1:16">
+      <c r="A978" s="1">
+        <v>1</v>
+      </c>
+      <c r="B978" t="s">
+        <v>223</v>
+      </c>
+      <c r="C978">
+        <v>6.150511064278188</v>
+      </c>
+      <c r="D978" t="s">
+        <v>464</v>
+      </c>
+      <c r="E978">
+        <v>6.274236037934668</v>
+      </c>
+      <c r="F978">
+        <v>1</v>
+      </c>
+      <c r="G978">
+        <v>0.004329488935721813</v>
+      </c>
+      <c r="H978">
+        <v>0.004325763962065332</v>
+      </c>
+      <c r="I978">
+        <v>0.1237249736564801</v>
+      </c>
+      <c r="J978">
+        <v>-0.02160168598524764</v>
+      </c>
+      <c r="K978">
+        <v>42.15</v>
+      </c>
+      <c r="L978">
+        <v>5.24</v>
+      </c>
+      <c r="M978">
+        <v>45.1</v>
+      </c>
+      <c r="N978">
+        <v>5.3</v>
+      </c>
+      <c r="O978">
+        <v>0</v>
+      </c>
+      <c r="P978" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="979" spans="1:16">
+      <c r="A979" s="1">
+        <v>0</v>
+      </c>
+      <c r="B979" t="s">
+        <v>222</v>
+      </c>
+      <c r="C979">
+        <v>5.32829599901169</v>
+      </c>
+      <c r="D979" t="s">
+        <v>464</v>
+      </c>
+      <c r="E979">
+        <v>5.374042056620847</v>
+      </c>
+      <c r="F979">
+        <v>1</v>
+      </c>
+      <c r="G979">
+        <v>0.005191704000988309</v>
+      </c>
+      <c r="H979">
+        <v>0.005225957943379153</v>
+      </c>
+      <c r="I979">
+        <v>0.04574605760915684</v>
+      </c>
+      <c r="J979">
+        <v>-0.00164173074547332</v>
+      </c>
+      <c r="K979">
+        <v>41.6</v>
+      </c>
+      <c r="L979">
+        <v>5.26</v>
+      </c>
+      <c r="M979">
+        <v>45.1</v>
+      </c>
+      <c r="N979">
+        <v>5.3</v>
+      </c>
+      <c r="O979">
+        <v>0</v>
+      </c>
+      <c r="P979" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="980" spans="1:16">
+      <c r="A980" s="1">
+        <v>1</v>
+      </c>
+      <c r="B980" t="s">
+        <v>223</v>
+      </c>
+      <c r="C980">
+        <v>5.309198950921701</v>
+      </c>
+      <c r="D980" t="s">
+        <v>464</v>
+      </c>
+      <c r="E980">
+        <v>5.374042056620847</v>
+      </c>
+      <c r="F980">
+        <v>1</v>
+      </c>
+      <c r="G980">
+        <v>0.0051708010490783</v>
+      </c>
+      <c r="H980">
+        <v>0.005225957943379153</v>
+      </c>
+      <c r="I980">
+        <v>0.06484310569914609</v>
+      </c>
+      <c r="J980">
+        <v>-0.00164173074547332</v>
+      </c>
+      <c r="K980">
+        <v>42.15</v>
+      </c>
+      <c r="L980">
+        <v>5.24</v>
+      </c>
+      <c r="M980">
+        <v>45.1</v>
+      </c>
+      <c r="N980">
+        <v>5.3</v>
+      </c>
+      <c r="O980">
+        <v>0</v>
+      </c>
+      <c r="P980" t="s">
+        <v>794</v>
       </c>
     </row>
   </sheetData>
